--- a/Auxiliary resources/MMCI Literature review matrices.xlsx
+++ b/Auxiliary resources/MMCI Literature review matrices.xlsx
@@ -8,18 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\Dissertation\Auxiliary resources\Matrix literature review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348DF7A5-1CA4-4A47-A036-D530E8B40462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1CC8BBD-3871-4A58-9F96-35FD0DC9FB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1EA815CA-3631-4EEA-BC35-EAE153F95668}"/>
   </bookViews>
   <sheets>
-    <sheet name="Complete matrix" sheetId="3" r:id="rId1"/>
+    <sheet name="Complete list" sheetId="3" r:id="rId1"/>
     <sheet name="Obi" sheetId="1" r:id="rId2"/>
     <sheet name="R-Peña" sheetId="7" r:id="rId3"/>
     <sheet name="Hoslednová" sheetId="9" r:id="rId4"/>
     <sheet name="Empirical problems" sheetId="6" r:id="rId5"/>
     <sheet name="Nomenclatures" sheetId="5" r:id="rId6"/>
-    <sheet name="Nussbaum's 10" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="371">
   <si>
     <t>Dimension</t>
   </si>
@@ -267,21 +266,6 @@
   </si>
   <si>
     <t>Relation with Nusbaum's original ten</t>
-  </si>
-  <si>
-    <t>Environmental security</t>
-  </si>
-  <si>
-    <t>Adequate livelihood</t>
-  </si>
-  <si>
-    <t>Access to healthcare</t>
-  </si>
-  <si>
-    <t>Political violence</t>
-  </si>
-  <si>
-    <t>Freedom from violence</t>
   </si>
   <si>
     <t>Nomenclature</t>
@@ -997,9 +981,6 @@
     <t>Variable</t>
   </si>
   <si>
-    <t>Number of meetings organized by the community</t>
-  </si>
-  <si>
     <t>Level MxFLS</t>
   </si>
   <si>
@@ -1012,9 +993,6 @@
     <t>It can erode capacity to stay</t>
   </si>
   <si>
-    <t>Organization of meetings</t>
-  </si>
-  <si>
     <t>MxFLS question</t>
   </si>
   <si>
@@ -1022,9 +1000,6 @@
   </si>
   <si>
     <t>AC01: Does this community organize activities, meetings or assemblies?</t>
-  </si>
-  <si>
-    <t>Active population attendance to community meetings</t>
   </si>
   <si>
     <t>Number of cooperatives in the community</t>
@@ -1181,6 +1156,27 @@
     <t>1. I need to calculate percentages for those that reported the quantitity
 2. I need to do the calculation in an individual level dataset
 3. I need to join the datasets and replace</t>
+  </si>
+  <si>
+    <t>Community meeting</t>
+  </si>
+  <si>
+    <t>Community meetings</t>
+  </si>
+  <si>
+    <t>The community organizes meetings</t>
+  </si>
+  <si>
+    <t>Activate population attendance to community meetings</t>
+  </si>
+  <si>
+    <t>Decision after cleaning in STATA</t>
+  </si>
+  <si>
+    <t>The variable is too noisy</t>
+  </si>
+  <si>
+    <t>No, the variable has many outliers, and people who did not report well</t>
   </si>
 </sst>
 </file>
@@ -1208,7 +1204,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1236,6 +1232,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1337,7 +1339,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1380,45 +1382,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1499,29 +1462,90 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Garamond"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2214,32 +2238,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{205A4EAD-79AC-46AE-89E1-8D7FFBE1AC1D}" name="Table1" displayName="Table1" ref="A1:T57" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21" tableBorderDxfId="20">
-  <autoFilter ref="A1:T57" xr:uid="{205A4EAD-79AC-46AE-89E1-8D7FFBE1AC1D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{205A4EAD-79AC-46AE-89E1-8D7FFBE1AC1D}" name="Table1" displayName="Table1" ref="A1:U57" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
+  <autoFilter ref="A1:U57" xr:uid="{205A4EAD-79AC-46AE-89E1-8D7FFBE1AC1D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R57">
     <sortCondition ref="A1:A57"/>
   </sortState>
-  <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{CBA470E9-2761-4E7B-95D5-EEA3137A21A6}" name="Nussbaum's capability domain" dataDxfId="19"/>
-    <tableColumn id="18" xr3:uid="{E49D1BA9-45F5-4866-9FC1-8B7D65B132BA}" name="Nussbaum's definition" dataDxfId="18"/>
-    <tableColumn id="14" xr3:uid="{9668895B-6A1F-46C1-9CB4-4EF8EDF7ACA8}" name="CA determinant" dataDxfId="17"/>
-    <tableColumn id="8" xr3:uid="{C85D8B0B-226A-4471-92F2-09021F6BB258}" name="Number" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{642A1707-42F2-4967-B446-AE1AC8011EBD}" name="Level MxFLS" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{5D94FE2C-CAC7-41EC-9236-BB9F6A0EFF94}" name="Study level dimension (Obi/R-Peña/Hosnedlova)" dataDxfId="14"/>
-    <tableColumn id="22" xr3:uid="{F3488BEE-30B3-4F02-9BD8-6A5BEB8BA4AF}" name="Schewel's dimensions" dataDxfId="13"/>
-    <tableColumn id="20" xr3:uid="{64ACCA7A-3E62-4C90-97FC-599C0A211D65}" name="Author" dataDxfId="12"/>
-    <tableColumn id="21" xr3:uid="{331ACB1B-F439-4A5A-95A8-F01B7FC11CB3}" name="Reference" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{9F13372D-BE7C-43DA-B27F-7E69A7AD803E}" name="Variable" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{82C2EF7E-7626-4535-AFEC-2650F35F7DB9}" name="Indicator" dataDxfId="9"/>
-    <tableColumn id="15" xr3:uid="{A9D86E20-5A8B-40AA-B391-65B5FD99ED4D}" name="Question (original author)" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{48D319ED-3810-41A9-AF63-BA4BF4E027F2}" name="MxFLS section" dataDxfId="7"/>
-    <tableColumn id="16" xr3:uid="{2AB760BD-7C92-4F25-AF7A-E2A52BFDE1FB}" name="MxFLS question" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{0C3128B9-5B21-45D0-AC3E-898982331141}" name="Capability to stay" dataDxfId="5"/>
-    <tableColumn id="7" xr3:uid="{2B387827-DEAE-4AA7-8AF0-103E8EC5EB2C}" name="Capabiltiy to leave" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{05332881-CA52-42D3-B038-B13CB02B4F0F}" name="Incorporation decision" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{06CB4C1D-8C05-4D74-9D76-48F61FE2E8A2}" name="Incorporation rule" dataDxfId="2"/>
-    <tableColumn id="23" xr3:uid="{6A38D615-E512-4599-8142-55B257B60373}" name="Cleaning in STATA" dataDxfId="1"/>
-    <tableColumn id="25" xr3:uid="{62C0414C-0F32-4965-9B86-352FF82B351F}" name="What remains to be done" dataDxfId="0"/>
+  <tableColumns count="21">
+    <tableColumn id="1" xr3:uid="{CBA470E9-2761-4E7B-95D5-EEA3137A21A6}" name="Nussbaum's capability domain" dataDxfId="20"/>
+    <tableColumn id="18" xr3:uid="{E49D1BA9-45F5-4866-9FC1-8B7D65B132BA}" name="Nussbaum's definition" dataDxfId="19"/>
+    <tableColumn id="14" xr3:uid="{9668895B-6A1F-46C1-9CB4-4EF8EDF7ACA8}" name="CA determinant" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{C85D8B0B-226A-4471-92F2-09021F6BB258}" name="Number" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{642A1707-42F2-4967-B446-AE1AC8011EBD}" name="Level MxFLS" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{5D94FE2C-CAC7-41EC-9236-BB9F6A0EFF94}" name="Study level dimension (Obi/R-Peña/Hosnedlova)" dataDxfId="15"/>
+    <tableColumn id="22" xr3:uid="{F3488BEE-30B3-4F02-9BD8-6A5BEB8BA4AF}" name="Schewel's dimensions" dataDxfId="14"/>
+    <tableColumn id="20" xr3:uid="{64ACCA7A-3E62-4C90-97FC-599C0A211D65}" name="Author" dataDxfId="13"/>
+    <tableColumn id="21" xr3:uid="{331ACB1B-F439-4A5A-95A8-F01B7FC11CB3}" name="Reference" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{9F13372D-BE7C-43DA-B27F-7E69A7AD803E}" name="Variable" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{82C2EF7E-7626-4535-AFEC-2650F35F7DB9}" name="Indicator" dataDxfId="10"/>
+    <tableColumn id="15" xr3:uid="{A9D86E20-5A8B-40AA-B391-65B5FD99ED4D}" name="Question (original author)" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{48D319ED-3810-41A9-AF63-BA4BF4E027F2}" name="MxFLS section" dataDxfId="8"/>
+    <tableColumn id="16" xr3:uid="{2AB760BD-7C92-4F25-AF7A-E2A52BFDE1FB}" name="MxFLS question" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{0C3128B9-5B21-45D0-AC3E-898982331141}" name="Capability to stay" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{2B387827-DEAE-4AA7-8AF0-103E8EC5EB2C}" name="Capabiltiy to leave" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{05332881-CA52-42D3-B038-B13CB02B4F0F}" name="Incorporation decision" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{06CB4C1D-8C05-4D74-9D76-48F61FE2E8A2}" name="Incorporation rule" dataDxfId="3"/>
+    <tableColumn id="23" xr3:uid="{6A38D615-E512-4599-8142-55B257B60373}" name="Cleaning in STATA" dataDxfId="2"/>
+    <tableColumn id="25" xr3:uid="{62C0414C-0F32-4965-9B86-352FF82B351F}" name="What remains to be done" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{42958CCE-6D89-442E-AA0F-AE71D7632606}" name="Decision after cleaning in STATA" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2562,261 +2587,270 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C6D3BA-C091-4098-987E-D59F3E361AAB}">
-  <dimension ref="A1:T57"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr defaultRowHeight="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" style="61" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="61" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="60" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" style="60" customWidth="1"/>
-    <col min="5" max="5" width="13" style="60" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" style="60" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="60" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" style="60" customWidth="1"/>
-    <col min="9" max="9" width="17" style="60" customWidth="1"/>
-    <col min="10" max="10" width="20" style="60" customWidth="1"/>
-    <col min="11" max="13" width="27.28515625" style="60" customWidth="1"/>
-    <col min="14" max="14" width="34.140625" style="60" customWidth="1"/>
-    <col min="15" max="15" width="29.28515625" style="61" customWidth="1"/>
-    <col min="16" max="16" width="21.85546875" style="61" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="61" customWidth="1"/>
-    <col min="18" max="18" width="23.140625" style="60" customWidth="1"/>
-    <col min="19" max="19" width="16.5703125" style="61" customWidth="1"/>
-    <col min="20" max="20" width="35" style="61" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" style="61" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="61"/>
+    <col min="1" max="1" width="15.140625" style="20" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" style="20" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="33" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" style="33" customWidth="1"/>
+    <col min="5" max="5" width="13" style="33" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" style="33" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="33" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" style="33" customWidth="1"/>
+    <col min="9" max="9" width="17" style="33" customWidth="1"/>
+    <col min="10" max="10" width="20" style="33" customWidth="1"/>
+    <col min="11" max="13" width="27.28515625" style="33" customWidth="1"/>
+    <col min="14" max="14" width="34.140625" style="33" customWidth="1"/>
+    <col min="15" max="15" width="29.28515625" style="20" customWidth="1"/>
+    <col min="16" max="16" width="21.85546875" style="20" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="20" customWidth="1"/>
+    <col min="18" max="18" width="23.140625" style="33" customWidth="1"/>
+    <col min="19" max="19" width="16.5703125" style="20" customWidth="1"/>
+    <col min="20" max="20" width="35" style="20" customWidth="1"/>
+    <col min="21" max="21" width="19.5703125" style="20" customWidth="1"/>
+    <col min="22" max="22" width="9.140625" style="20" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>314</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>326</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="K1" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="N1" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="O1" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q1" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="R1" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="S1" s="46" t="s">
+        <v>331</v>
+      </c>
+      <c r="T1" s="44" t="s">
+        <v>362</v>
+      </c>
+      <c r="U1" s="44" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>316</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>307</v>
+      </c>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="M2" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="N2" s="18" t="s">
+        <v>312</v>
+      </c>
+      <c r="O2" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="R2" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="S2" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="T2" s="21"/>
+      <c r="U2" s="21"/>
+    </row>
+    <row r="3" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="60" t="s">
+        <v>266</v>
+      </c>
+      <c r="B3" s="60" t="s">
+        <v>288</v>
+      </c>
+      <c r="C3" s="61" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="61" t="s">
+        <v>317</v>
+      </c>
+      <c r="E3" s="61" t="s">
+        <v>307</v>
+      </c>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="60" t="s">
+        <v>325</v>
+      </c>
+      <c r="I3" s="60" t="s">
+        <v>168</v>
+      </c>
+      <c r="J3" s="61" t="s">
+        <v>365</v>
+      </c>
+      <c r="K3" s="61" t="s">
+        <v>367</v>
+      </c>
+      <c r="L3" s="61" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3" s="61" t="s">
+        <v>320</v>
+      </c>
+      <c r="N3" s="61" t="s">
         <v>322</v>
       </c>
-      <c r="B1" s="54" t="s">
-        <v>290</v>
-      </c>
-      <c r="C1" s="32" t="s">
-        <v>323</v>
-      </c>
-      <c r="D1" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="E1" s="32" t="s">
-        <v>312</v>
-      </c>
-      <c r="F1" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="G1" s="32" t="s">
-        <v>331</v>
-      </c>
-      <c r="H1" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="32" t="s">
+      <c r="O3" s="61"/>
+      <c r="P3" s="60"/>
+      <c r="Q3" s="60" t="s">
+        <v>174</v>
+      </c>
+      <c r="R3" s="62" t="s">
+        <v>370</v>
+      </c>
+      <c r="S3" s="63" t="s">
+        <v>333</v>
+      </c>
+      <c r="T3" s="61" t="s">
+        <v>363</v>
+      </c>
+      <c r="U3" s="61" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>307</v>
+      </c>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="I4" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="K4" s="18" t="s">
+        <v>313</v>
+      </c>
+      <c r="L4" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="N4" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="O4" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="P4" s="21"/>
+      <c r="Q4" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="R4" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="S4" s="29" t="s">
         <v>334</v>
       </c>
-      <c r="J1" s="32" t="s">
-        <v>310</v>
-      </c>
-      <c r="K1" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="L1" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="M1" s="32" t="s">
-        <v>318</v>
-      </c>
-      <c r="N1" s="32" t="s">
-        <v>317</v>
-      </c>
-      <c r="O1" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="P1" s="32" t="s">
-        <v>215</v>
-      </c>
-      <c r="Q1" s="32" t="s">
-        <v>278</v>
-      </c>
-      <c r="R1" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="S1" s="62" t="s">
-        <v>339</v>
-      </c>
-      <c r="T1" s="58" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
-        <v>271</v>
-      </c>
-      <c r="B2" s="34" t="s">
-        <v>293</v>
-      </c>
-      <c r="C2" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="31" t="s">
-        <v>324</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>313</v>
-      </c>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="I2" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="J2" s="31" t="s">
-        <v>316</v>
-      </c>
-      <c r="K2" s="31" t="s">
-        <v>311</v>
-      </c>
-      <c r="L2" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="M2" s="31" t="s">
-        <v>328</v>
-      </c>
-      <c r="N2" s="31" t="s">
-        <v>319</v>
-      </c>
-      <c r="O2" s="31" t="s">
-        <v>335</v>
-      </c>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="R2" s="35" t="s">
-        <v>287</v>
-      </c>
-      <c r="S2" s="42" t="s">
-        <v>340</v>
-      </c>
-      <c r="T2" s="34"/>
-    </row>
-    <row r="3" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="34" t="s">
-        <v>271</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>293</v>
-      </c>
-      <c r="C3" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="31" t="s">
-        <v>325</v>
-      </c>
-      <c r="E3" s="31" t="s">
-        <v>313</v>
-      </c>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="I3" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="J3" s="31" t="s">
-        <v>316</v>
-      </c>
-      <c r="K3" s="31" t="s">
-        <v>320</v>
-      </c>
-      <c r="L3" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="M3" s="31" t="s">
-        <v>328</v>
-      </c>
-      <c r="N3" s="31" t="s">
-        <v>330</v>
-      </c>
-      <c r="O3" s="31"/>
-      <c r="P3" s="34"/>
-      <c r="Q3" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="R3" s="35" t="s">
-        <v>287</v>
-      </c>
-      <c r="S3" s="42" t="s">
-        <v>341</v>
-      </c>
-      <c r="T3" s="31" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="34" t="s">
-        <v>271</v>
-      </c>
-      <c r="B4" s="34" t="s">
-        <v>293</v>
-      </c>
-      <c r="C4" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="31" t="s">
-        <v>326</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>313</v>
-      </c>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="34" t="s">
-        <v>333</v>
-      </c>
-      <c r="I4" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="J4" s="31" t="s">
-        <v>246</v>
-      </c>
-      <c r="K4" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="L4" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="M4" s="31" t="s">
-        <v>327</v>
-      </c>
-      <c r="N4" s="31" t="s">
-        <v>329</v>
-      </c>
-      <c r="O4" s="31" t="s">
-        <v>247</v>
-      </c>
-      <c r="P4" s="34"/>
-      <c r="Q4" s="34" t="s">
-        <v>111</v>
-      </c>
-      <c r="R4" s="35" t="s">
-        <v>287</v>
-      </c>
-      <c r="S4" s="42" t="s">
-        <v>342</v>
-      </c>
-      <c r="T4" s="34"/>
-    </row>
-    <row r="5" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T4" s="21"/>
+      <c r="U4" s="21"/>
+    </row>
+    <row r="5" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>48</v>
@@ -2830,10 +2864,10 @@
       </c>
       <c r="G5" s="16"/>
       <c r="H5" s="17" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="J5" s="16" t="s">
         <v>6</v>
@@ -2845,10 +2879,10 @@
         <v>31</v>
       </c>
       <c r="M5" s="16" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="N5" s="16" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="O5" s="16" t="s">
         <v>51</v>
@@ -2857,22 +2891,23 @@
         <v>51</v>
       </c>
       <c r="Q5" s="16" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="R5" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="S5" s="56" t="s">
-        <v>343</v>
+        <v>358</v>
+      </c>
+      <c r="S5" s="43" t="s">
+        <v>335</v>
       </c>
       <c r="T5" s="16"/>
-    </row>
-    <row r="6" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U5" s="16"/>
+    </row>
+    <row r="6" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>57</v>
@@ -2886,10 +2921,10 @@
       </c>
       <c r="G6" s="16"/>
       <c r="H6" s="17" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="J6" s="17" t="s">
         <v>7</v>
@@ -2901,10 +2936,10 @@
         <v>32</v>
       </c>
       <c r="M6" s="16" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="N6" s="16" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="O6" s="16" t="s">
         <v>51</v>
@@ -2912,115 +2947,118 @@
       <c r="P6" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="Q6" s="36" t="s">
-        <v>179</v>
+      <c r="Q6" s="23" t="s">
+        <v>174</v>
       </c>
       <c r="R6" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="S6" s="36" t="s">
-        <v>343</v>
+        <v>358</v>
+      </c>
+      <c r="S6" s="23" t="s">
+        <v>335</v>
       </c>
       <c r="T6" s="16"/>
-    </row>
-    <row r="7" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="37" t="s">
-        <v>271</v>
-      </c>
-      <c r="B7" s="37" t="s">
-        <v>293</v>
-      </c>
-      <c r="C7" s="38" t="s">
+      <c r="U6" s="16"/>
+    </row>
+    <row r="7" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38" t="s">
-        <v>233</v>
-      </c>
-      <c r="K7" s="38"/>
-      <c r="L7" s="38" t="s">
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="39" t="s">
-        <v>178</v>
-      </c>
-      <c r="R7" s="40" t="s">
-        <v>367</v>
-      </c>
-      <c r="S7" s="39"/>
-      <c r="T7" s="37"/>
-    </row>
-    <row r="8" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="34" t="s">
-        <v>271</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>296</v>
-      </c>
-      <c r="C8" s="31" t="s">
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="R7" s="27" t="s">
+        <v>359</v>
+      </c>
+      <c r="S7" s="26"/>
+      <c r="T7" s="24"/>
+      <c r="U7" s="24"/>
+    </row>
+    <row r="8" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="C8" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31" t="s">
+      <c r="D8" s="18"/>
+      <c r="E8" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="F8" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="G8" s="31"/>
-      <c r="H8" s="31" t="s">
-        <v>336</v>
-      </c>
-      <c r="I8" s="34" t="s">
-        <v>275</v>
-      </c>
-      <c r="J8" s="34" t="s">
+      <c r="F8" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="J8" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="K8" s="34" t="s">
+      <c r="K8" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="L8" s="31" t="s">
+      <c r="L8" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="M8" s="31" t="s">
-        <v>338</v>
-      </c>
-      <c r="N8" s="31" t="s">
-        <v>337</v>
-      </c>
-      <c r="O8" s="34" t="s">
+      <c r="M8" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="N8" s="18" t="s">
+        <v>329</v>
+      </c>
+      <c r="O8" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="P8" s="34" t="s">
+      <c r="P8" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="Q8" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="R8" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="S8" s="42" t="s">
-        <v>342</v>
-      </c>
-      <c r="T8" s="34"/>
-    </row>
-    <row r="9" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q8" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="R8" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="S8" s="29" t="s">
+        <v>334</v>
+      </c>
+      <c r="T8" s="21"/>
+      <c r="U8" s="21"/>
+    </row>
+    <row r="9" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>50</v>
@@ -3030,14 +3068,14 @@
         <v>55</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G9" s="17"/>
       <c r="H9" s="17" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="J9" s="16" t="s">
         <v>13</v>
@@ -3050,7 +3088,7 @@
       </c>
       <c r="M9" s="16"/>
       <c r="N9" s="16" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="O9" s="16" t="s">
         <v>51</v>
@@ -3058,596 +3096,609 @@
       <c r="P9" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="Q9" s="36" t="s">
-        <v>179</v>
+      <c r="Q9" s="23" t="s">
+        <v>174</v>
       </c>
       <c r="R9" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="S9" s="56"/>
+        <v>358</v>
+      </c>
+      <c r="S9" s="43"/>
       <c r="T9" s="16"/>
-    </row>
-    <row r="10" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="34" t="s">
-        <v>268</v>
-      </c>
-      <c r="B10" s="34" t="s">
+      <c r="U9" s="16"/>
+    </row>
+    <row r="10" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>339</v>
+      </c>
+      <c r="K10" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="N10" s="18" t="s">
+        <v>343</v>
+      </c>
+      <c r="O10" s="21"/>
+      <c r="P10" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q10" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="R10" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="S10" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="T10" s="18"/>
+      <c r="U10" s="18"/>
+    </row>
+    <row r="11" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="I11" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>339</v>
+      </c>
+      <c r="K11" s="18" t="s">
+        <v>341</v>
+      </c>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="N11" s="18" t="s">
+        <v>342</v>
+      </c>
+      <c r="O11" s="21"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="R11" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="S11" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="T11" s="18"/>
+      <c r="U11" s="18"/>
+    </row>
+    <row r="12" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="I12" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>339</v>
+      </c>
+      <c r="K12" s="18" t="s">
+        <v>345</v>
+      </c>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="N12" s="18" t="s">
+        <v>344</v>
+      </c>
+      <c r="O12" s="21"/>
+      <c r="P12" s="18"/>
+      <c r="Q12" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="R12" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="S12" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="T12" s="18"/>
+      <c r="U12" s="18"/>
+    </row>
+    <row r="13" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="I13" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>339</v>
+      </c>
+      <c r="K13" s="18" t="s">
+        <v>349</v>
+      </c>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="N13" s="18" t="s">
+        <v>350</v>
+      </c>
+      <c r="O13" s="21"/>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="R13" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="S13" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="T13" s="18"/>
+      <c r="U13" s="18"/>
+    </row>
+    <row r="14" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>348</v>
+      </c>
+      <c r="K14" s="18" t="s">
+        <v>346</v>
+      </c>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="N14" s="18" t="s">
+        <v>347</v>
+      </c>
+      <c r="O14" s="21"/>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="R14" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="S14" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="T14" s="18"/>
+      <c r="U14" s="18"/>
+    </row>
+    <row r="15" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="I15" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="J15" s="25" t="s">
+        <v>351</v>
+      </c>
+      <c r="K15" s="25" t="s">
+        <v>351</v>
+      </c>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25" t="s">
+        <v>338</v>
+      </c>
+      <c r="N15" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="O15" s="24"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="R15" s="25" t="s">
+        <v>353</v>
+      </c>
+      <c r="S15" s="26"/>
+      <c r="T15" s="24"/>
+      <c r="U15" s="24"/>
+    </row>
+    <row r="16" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="I16" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="J16" s="25" t="s">
+        <v>354</v>
+      </c>
+      <c r="K16" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25" t="s">
+        <v>338</v>
+      </c>
+      <c r="N16" s="25" t="s">
+        <v>356</v>
+      </c>
+      <c r="O16" s="24"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="R16" s="25" t="s">
+        <v>357</v>
+      </c>
+      <c r="S16" s="26"/>
+      <c r="T16" s="24"/>
+      <c r="U16" s="24"/>
+    </row>
+    <row r="17" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="J17" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="K17" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18" t="s">
+        <v>360</v>
+      </c>
+      <c r="N17" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="O17" s="21"/>
+      <c r="P17" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q17" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="R17" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="S17" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="T17" s="18"/>
+      <c r="U17" s="18"/>
+    </row>
+    <row r="18" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="I18" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="J18" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>337</v>
+      </c>
+      <c r="L18" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="O18" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="P18" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q18" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="R18" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="S18" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="T18" s="18"/>
+      <c r="U18" s="18"/>
+    </row>
+    <row r="19" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>294</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="J19" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="24"/>
+      <c r="L19" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="M19" s="25"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="P19" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q19" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="R19" s="25"/>
+      <c r="S19" s="26"/>
+      <c r="T19" s="24"/>
+      <c r="U19" s="24"/>
+    </row>
+    <row r="20" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>294</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="C10" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31" t="s">
-        <v>333</v>
-      </c>
-      <c r="I10" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="J10" s="31" t="s">
-        <v>347</v>
-      </c>
-      <c r="K10" s="31" t="s">
-        <v>348</v>
-      </c>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31" t="s">
-        <v>346</v>
-      </c>
-      <c r="N10" s="31" t="s">
-        <v>351</v>
-      </c>
-      <c r="O10" s="34"/>
-      <c r="P10" s="31" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q10" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="R10" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="S10" s="35" t="s">
-        <v>342</v>
-      </c>
-      <c r="T10" s="31"/>
-    </row>
-    <row r="11" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="34" t="s">
-        <v>268</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>297</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="31"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31" t="s">
-        <v>333</v>
-      </c>
-      <c r="I11" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="J11" s="31" t="s">
-        <v>347</v>
-      </c>
-      <c r="K11" s="31" t="s">
-        <v>349</v>
-      </c>
-      <c r="L11" s="31"/>
-      <c r="M11" s="31" t="s">
-        <v>346</v>
-      </c>
-      <c r="N11" s="31" t="s">
-        <v>350</v>
-      </c>
-      <c r="O11" s="34"/>
-      <c r="P11" s="31"/>
-      <c r="Q11" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="R11" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="S11" s="35" t="s">
-        <v>342</v>
-      </c>
-      <c r="T11" s="31"/>
-    </row>
-    <row r="12" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="34" t="s">
-        <v>268</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>297</v>
-      </c>
-      <c r="C12" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="31"/>
-      <c r="E12" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-      <c r="H12" s="31" t="s">
-        <v>333</v>
-      </c>
-      <c r="I12" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="J12" s="31" t="s">
-        <v>347</v>
-      </c>
-      <c r="K12" s="31" t="s">
-        <v>353</v>
-      </c>
-      <c r="L12" s="31"/>
-      <c r="M12" s="31" t="s">
-        <v>346</v>
-      </c>
-      <c r="N12" s="31" t="s">
-        <v>352</v>
-      </c>
-      <c r="O12" s="34"/>
-      <c r="P12" s="31"/>
-      <c r="Q12" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="R12" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="S12" s="35" t="s">
-        <v>342</v>
-      </c>
-      <c r="T12" s="31"/>
-    </row>
-    <row r="13" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="34" t="s">
-        <v>268</v>
-      </c>
-      <c r="B13" s="34" t="s">
-        <v>297</v>
-      </c>
-      <c r="C13" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31" t="s">
-        <v>333</v>
-      </c>
-      <c r="I13" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="J13" s="31" t="s">
-        <v>347</v>
-      </c>
-      <c r="K13" s="31" t="s">
-        <v>357</v>
-      </c>
-      <c r="L13" s="31"/>
-      <c r="M13" s="31" t="s">
-        <v>346</v>
-      </c>
-      <c r="N13" s="31" t="s">
-        <v>358</v>
-      </c>
-      <c r="O13" s="34"/>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="R13" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="S13" s="35" t="s">
-        <v>342</v>
-      </c>
-      <c r="T13" s="31"/>
-    </row>
-    <row r="14" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="34" t="s">
-        <v>268</v>
-      </c>
-      <c r="B14" s="34" t="s">
-        <v>297</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31" t="s">
-        <v>333</v>
-      </c>
-      <c r="I14" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="J14" s="31" t="s">
-        <v>356</v>
-      </c>
-      <c r="K14" s="31" t="s">
-        <v>354</v>
-      </c>
-      <c r="L14" s="31"/>
-      <c r="M14" s="31" t="s">
-        <v>346</v>
-      </c>
-      <c r="N14" s="31" t="s">
-        <v>355</v>
-      </c>
-      <c r="O14" s="34"/>
-      <c r="P14" s="31"/>
-      <c r="Q14" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="R14" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="S14" s="35" t="s">
-        <v>342</v>
-      </c>
-      <c r="T14" s="31"/>
-    </row>
-    <row r="15" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="B15" s="37" t="s">
-        <v>297</v>
-      </c>
-      <c r="C15" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="38"/>
-      <c r="E15" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="38"/>
-      <c r="G15" s="38"/>
-      <c r="H15" s="38" t="s">
-        <v>333</v>
-      </c>
-      <c r="I15" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="J15" s="38" t="s">
-        <v>359</v>
-      </c>
-      <c r="K15" s="38" t="s">
-        <v>359</v>
-      </c>
-      <c r="L15" s="38"/>
-      <c r="M15" s="38" t="s">
-        <v>346</v>
-      </c>
-      <c r="N15" s="38" t="s">
-        <v>360</v>
-      </c>
-      <c r="O15" s="37"/>
-      <c r="P15" s="38"/>
-      <c r="Q15" s="39" t="s">
-        <v>178</v>
-      </c>
-      <c r="R15" s="38" t="s">
-        <v>361</v>
-      </c>
-      <c r="S15" s="39"/>
-      <c r="T15" s="37"/>
-    </row>
-    <row r="16" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
-        <v>268</v>
-      </c>
-      <c r="B16" s="37" t="s">
-        <v>297</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="38"/>
-      <c r="E16" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="38"/>
-      <c r="G16" s="38"/>
-      <c r="H16" s="38" t="s">
-        <v>333</v>
-      </c>
-      <c r="I16" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="J16" s="38" t="s">
-        <v>362</v>
-      </c>
-      <c r="K16" s="38" t="s">
-        <v>363</v>
-      </c>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38" t="s">
-        <v>346</v>
-      </c>
-      <c r="N16" s="38" t="s">
-        <v>364</v>
-      </c>
-      <c r="O16" s="37"/>
-      <c r="P16" s="38"/>
-      <c r="Q16" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="R16" s="38" t="s">
-        <v>365</v>
-      </c>
-      <c r="S16" s="39"/>
-      <c r="T16" s="37"/>
-    </row>
-    <row r="17" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="34" t="s">
-        <v>268</v>
-      </c>
-      <c r="B17" s="34" t="s">
-        <v>297</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31" t="s">
-        <v>333</v>
-      </c>
-      <c r="I17" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="J17" s="31" t="s">
-        <v>261</v>
-      </c>
-      <c r="K17" s="31" t="s">
-        <v>344</v>
-      </c>
-      <c r="L17" s="31"/>
-      <c r="M17" s="31" t="s">
-        <v>368</v>
-      </c>
-      <c r="N17" s="31" t="s">
-        <v>369</v>
-      </c>
-      <c r="O17" s="34"/>
-      <c r="P17" s="31" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q17" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="R17" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="S17" s="35" t="s">
-        <v>342</v>
-      </c>
-      <c r="T17" s="31"/>
-    </row>
-    <row r="18" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="31" t="s">
-        <v>268</v>
-      </c>
-      <c r="B18" s="34" t="s">
-        <v>297</v>
-      </c>
-      <c r="C18" s="31" t="s">
-        <v>181</v>
-      </c>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31" t="s">
-        <v>336</v>
-      </c>
-      <c r="I18" s="34" t="s">
-        <v>275</v>
-      </c>
-      <c r="J18" s="31" t="s">
-        <v>274</v>
-      </c>
-      <c r="K18" s="31" t="s">
-        <v>345</v>
-      </c>
-      <c r="L18" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="M18" s="31"/>
-      <c r="N18" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="O18" s="34" t="s">
-        <v>26</v>
-      </c>
-      <c r="P18" s="34" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q18" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="R18" s="31" t="s">
-        <v>277</v>
-      </c>
-      <c r="S18" s="35" t="s">
-        <v>342</v>
-      </c>
-      <c r="T18" s="31"/>
-    </row>
-    <row r="19" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="37" t="s">
-        <v>166</v>
-      </c>
-      <c r="B19" s="55" t="s">
-        <v>299</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="38" t="s">
+      <c r="J20" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="O20" s="21"/>
+      <c r="P20" s="21"/>
+      <c r="Q20" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="R20" s="18" t="s">
+        <v>272</v>
+      </c>
+      <c r="S20" s="29"/>
+      <c r="T20" s="21"/>
+      <c r="U20" s="21"/>
+    </row>
+    <row r="21" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="B21" s="42" t="s">
+        <v>294</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="37" t="s">
-        <v>275</v>
-      </c>
-      <c r="J19" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K19" s="37"/>
-      <c r="L19" s="38" t="s">
-        <v>44</v>
-      </c>
-      <c r="M19" s="38"/>
-      <c r="N19" s="38"/>
-      <c r="O19" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="P19" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q19" s="39" t="s">
-        <v>179</v>
-      </c>
-      <c r="R19" s="38"/>
-      <c r="S19" s="39"/>
-      <c r="T19" s="37"/>
-    </row>
-    <row r="20" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="B20" s="48" t="s">
-        <v>299</v>
-      </c>
-      <c r="C20" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="34" t="s">
-        <v>302</v>
-      </c>
-      <c r="J20" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="M20" s="31"/>
-      <c r="N20" s="31" t="s">
-        <v>301</v>
-      </c>
-      <c r="O20" s="34"/>
-      <c r="P20" s="34"/>
-      <c r="Q20" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="R20" s="31" t="s">
-        <v>277</v>
-      </c>
-      <c r="S20" s="42"/>
-      <c r="T20" s="34"/>
-    </row>
-    <row r="21" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="37" t="s">
-        <v>166</v>
-      </c>
-      <c r="B21" s="55" t="s">
-        <v>299</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="38" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21" s="38"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="J21" s="38" t="s">
-        <v>182</v>
-      </c>
-      <c r="K21" s="38"/>
-      <c r="L21" s="38"/>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37" t="s">
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="J21" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="24"/>
+      <c r="N21" s="24"/>
+      <c r="O21" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="P21" s="37" t="s">
+      <c r="P21" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="Q21" s="39" t="s">
+      <c r="Q21" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="R21" s="38"/>
-      <c r="S21" s="39"/>
-      <c r="T21" s="37"/>
-    </row>
-    <row r="22" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R21" s="25"/>
+      <c r="S21" s="26"/>
+      <c r="T21" s="24"/>
+      <c r="U21" s="24"/>
+    </row>
+    <row r="22" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16" t="s">
-        <v>300</v>
-      </c>
-      <c r="B22" s="56" t="s">
-        <v>299</v>
+        <v>295</v>
+      </c>
+      <c r="B22" s="43" t="s">
+        <v>294</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="45"/>
-      <c r="E22" s="45"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
       <c r="F22" s="17" t="s">
         <v>17</v>
       </c>
       <c r="G22" s="17"/>
       <c r="H22" s="17"/>
       <c r="I22" s="16" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>14</v>
@@ -3658,207 +3709,212 @@
       </c>
       <c r="M22" s="16"/>
       <c r="N22" s="16" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="O22" s="16"/>
       <c r="P22" s="16"/>
-      <c r="Q22" s="36" t="s">
-        <v>179</v>
+      <c r="Q22" s="23" t="s">
+        <v>174</v>
       </c>
       <c r="R22" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="S22" s="41"/>
+        <v>358</v>
+      </c>
+      <c r="S22" s="28"/>
       <c r="T22" s="17"/>
-    </row>
-    <row r="23" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="31" t="s">
+      <c r="U22" s="17"/>
+    </row>
+    <row r="23" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>300</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="O23" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="P23" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="Q23" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="R23" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="B23" s="48" t="s">
-        <v>305</v>
-      </c>
-      <c r="C23" s="31" t="s">
-        <v>181</v>
-      </c>
-      <c r="D23" s="44"/>
-      <c r="E23" s="44" t="s">
+      <c r="S23" s="29"/>
+      <c r="T23" s="21"/>
+      <c r="U23" s="21"/>
+    </row>
+    <row r="24" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="F23" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="G23" s="31"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="K23" s="31"/>
-      <c r="L23" s="31" t="s">
+      <c r="F24" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="J24" s="18" t="s">
+        <v>268</v>
+      </c>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="M23" s="31"/>
-      <c r="N23" s="31" t="s">
-        <v>280</v>
-      </c>
-      <c r="O23" s="31" t="s">
-        <v>286</v>
-      </c>
-      <c r="P23" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="Q23" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="R23" s="31" t="s">
+      <c r="M24" s="18"/>
+      <c r="N24" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="O24" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="P24" s="18" t="s">
         <v>277</v>
       </c>
-      <c r="S23" s="42"/>
-      <c r="T23" s="34"/>
-    </row>
-    <row r="24" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="31" t="s">
+      <c r="Q24" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="R24" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="B24" s="34" t="s">
-        <v>305</v>
-      </c>
-      <c r="C24" s="31" t="s">
+      <c r="S24" s="29"/>
+      <c r="T24" s="21"/>
+      <c r="U24" s="21"/>
+    </row>
+    <row r="25" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="C25" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="F24" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="J24" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31" t="s">
+      <c r="D25" s="18"/>
+      <c r="E25" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="J25" s="18" t="s">
+        <v>265</v>
+      </c>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="O25" s="18"/>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="R25" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="S25" s="29"/>
+      <c r="T25" s="21"/>
+      <c r="U25" s="21"/>
+    </row>
+    <row r="26" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="18"/>
+      <c r="E26" s="31" t="s">
+        <v>307</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="J26" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="M24" s="31"/>
-      <c r="N24" s="31" t="s">
-        <v>280</v>
-      </c>
-      <c r="O24" s="31" t="s">
-        <v>281</v>
-      </c>
-      <c r="P24" s="31" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q24" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="R24" s="31" t="s">
-        <v>277</v>
-      </c>
-      <c r="S24" s="42"/>
-      <c r="T24" s="34"/>
-    </row>
-    <row r="25" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="31" t="s">
-        <v>303</v>
-      </c>
-      <c r="B25" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="31"/>
-      <c r="E25" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="F25" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="J25" s="31" t="s">
-        <v>270</v>
-      </c>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="31"/>
-      <c r="N25" s="31" t="s">
-        <v>111</v>
-      </c>
-      <c r="O25" s="31"/>
-      <c r="P25" s="31"/>
-      <c r="Q25" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="R25" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="S25" s="42"/>
-      <c r="T25" s="34"/>
-    </row>
-    <row r="26" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="31" t="s">
-        <v>303</v>
-      </c>
-      <c r="B26" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="C26" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="31"/>
-      <c r="E26" s="44" t="s">
-        <v>313</v>
-      </c>
-      <c r="F26" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="J26" s="31" t="s">
-        <v>242</v>
-      </c>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31" t="s">
-        <v>244</v>
-      </c>
-      <c r="O26" s="31" t="s">
-        <v>243</v>
-      </c>
-      <c r="P26" s="34"/>
-      <c r="Q26" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="R26" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="S26" s="42"/>
-      <c r="T26" s="34"/>
-    </row>
-    <row r="27" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M26" s="18"/>
+      <c r="N26" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="O26" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="R26" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="S26" s="29"/>
+      <c r="T26" s="21"/>
+      <c r="U26" s="21"/>
+    </row>
+    <row r="27" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C27" s="17" t="s">
         <v>50</v>
@@ -3866,197 +3922,200 @@
       <c r="D27" s="17"/>
       <c r="E27" s="17"/>
       <c r="F27" s="17" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G27" s="17"/>
       <c r="H27" s="17"/>
       <c r="I27" s="17" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="K27" s="17"/>
       <c r="L27" s="17"/>
       <c r="M27" s="16"/>
       <c r="N27" s="16" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="O27" s="16"/>
       <c r="P27" s="17" t="s">
-        <v>309</v>
-      </c>
-      <c r="Q27" s="41" t="s">
-        <v>179</v>
+        <v>304</v>
+      </c>
+      <c r="Q27" s="28" t="s">
+        <v>174</v>
       </c>
       <c r="R27" s="17"/>
-      <c r="S27" s="41"/>
+      <c r="S27" s="28"/>
       <c r="T27" s="17"/>
-    </row>
-    <row r="28" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="31" t="s">
+      <c r="U27" s="17"/>
+    </row>
+    <row r="28" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="J28" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="K28" s="18"/>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="N28" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="O28" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="P28" s="21"/>
+      <c r="Q28" s="22"/>
+      <c r="R28" s="18"/>
+      <c r="S28" s="29"/>
+      <c r="T28" s="21"/>
+      <c r="U28" s="21"/>
+    </row>
+    <row r="29" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="B29" s="42" t="s">
         <v>303</v>
       </c>
-      <c r="B28" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="C28" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31" t="s">
-        <v>167</v>
-      </c>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="J28" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31" t="s">
-        <v>307</v>
-      </c>
-      <c r="N28" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="O28" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="35"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="42"/>
-      <c r="T28" s="34"/>
-    </row>
-    <row r="29" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="38" t="s">
-        <v>272</v>
-      </c>
-      <c r="B29" s="55" t="s">
-        <v>308</v>
-      </c>
-      <c r="C29" s="38" t="s">
+      <c r="C29" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="38" t="s">
-        <v>217</v>
-      </c>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="37" t="s">
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="J29" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="24"/>
+      <c r="N29" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="O29" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="P29" s="24"/>
+      <c r="Q29" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="J29" s="38" t="s">
-        <v>225</v>
-      </c>
-      <c r="K29" s="38"/>
-      <c r="L29" s="38"/>
-      <c r="M29" s="37"/>
-      <c r="N29" s="37" t="s">
-        <v>228</v>
-      </c>
-      <c r="O29" s="38" t="s">
-        <v>227</v>
-      </c>
-      <c r="P29" s="37"/>
-      <c r="Q29" s="39" t="s">
-        <v>178</v>
-      </c>
-      <c r="R29" s="38"/>
-      <c r="S29" s="40"/>
-      <c r="T29" s="38"/>
-    </row>
-    <row r="30" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="46" t="s">
-        <v>272</v>
-      </c>
-      <c r="B30" s="57" t="s">
-        <v>272</v>
+      <c r="R29" s="25"/>
+      <c r="S29" s="27"/>
+      <c r="T29" s="25"/>
+      <c r="U29" s="25"/>
+    </row>
+    <row r="30" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="33" t="s">
+        <v>267</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>267</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="D30" s="46"/>
-      <c r="E30" s="46"/>
       <c r="F30" s="11" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G30" s="11"/>
       <c r="H30" s="11"/>
       <c r="I30" s="14" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="K30" s="11"/>
       <c r="L30" s="11"/>
       <c r="M30" s="11"/>
       <c r="N30" s="11" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="O30" s="11" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="P30" s="14"/>
-      <c r="Q30" s="47"/>
+      <c r="Q30" s="34"/>
       <c r="R30" s="11"/>
-      <c r="S30" s="47"/>
+      <c r="S30" s="34"/>
       <c r="T30" s="14"/>
-    </row>
-    <row r="31" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="48" t="s">
+      <c r="U30" s="14"/>
+    </row>
+    <row r="31" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="35" t="s">
+        <v>284</v>
+      </c>
+      <c r="B31" s="21" t="s">
         <v>289</v>
       </c>
-      <c r="B31" s="34" t="s">
-        <v>294</v>
-      </c>
-      <c r="C31" s="31" t="s">
+      <c r="C31" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="G31" s="31"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="34" t="s">
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="K31" s="34"/>
-      <c r="L31" s="31" t="s">
+      <c r="K31" s="21"/>
+      <c r="L31" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="M31" s="31"/>
-      <c r="N31" s="31" t="s">
-        <v>298</v>
-      </c>
-      <c r="O31" s="34" t="s">
+      <c r="M31" s="18"/>
+      <c r="N31" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="O31" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="P31" s="34" t="s">
+      <c r="P31" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="Q31" s="42"/>
-      <c r="R31" s="31"/>
-      <c r="S31" s="42"/>
-      <c r="T31" s="34"/>
-    </row>
-    <row r="32" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q31" s="29"/>
+      <c r="R31" s="18"/>
+      <c r="S31" s="29"/>
+      <c r="T31" s="21"/>
+      <c r="U31" s="21"/>
+    </row>
+    <row r="32" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="16" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C32" s="17" t="s">
         <v>50</v>
@@ -4064,12 +4123,12 @@
       <c r="D32" s="17"/>
       <c r="E32" s="17"/>
       <c r="F32" s="17" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G32" s="17"/>
       <c r="H32" s="17"/>
       <c r="I32" s="16" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="J32" s="16" t="s">
         <v>11</v>
@@ -4086,19 +4145,20 @@
       <c r="P32" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="Q32" s="36" t="s">
-        <v>179</v>
+      <c r="Q32" s="23" t="s">
+        <v>174</v>
       </c>
       <c r="R32" s="17"/>
-      <c r="S32" s="41"/>
+      <c r="S32" s="28"/>
       <c r="T32" s="17"/>
-    </row>
-    <row r="33" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U32" s="17"/>
+    </row>
+    <row r="33" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="16" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C33" s="17" t="s">
         <v>48</v>
@@ -4106,7 +4166,7 @@
       <c r="D33" s="17"/>
       <c r="E33" s="17"/>
       <c r="F33" s="17" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G33" s="17"/>
       <c r="H33" s="17"/>
@@ -4120,25 +4180,26 @@
       </c>
       <c r="M33" s="16"/>
       <c r="N33" s="16" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="O33" s="16" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="P33" s="16"/>
-      <c r="Q33" s="36"/>
+      <c r="Q33" s="23"/>
       <c r="R33" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="S33" s="41"/>
+        <v>234</v>
+      </c>
+      <c r="S33" s="28"/>
       <c r="T33" s="17"/>
-    </row>
-    <row r="34" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U33" s="17"/>
+    </row>
+    <row r="34" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="16" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="C34" s="17" t="s">
         <v>47</v>
@@ -4146,12 +4207,12 @@
       <c r="D34" s="17"/>
       <c r="E34" s="17"/>
       <c r="F34" s="16" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G34" s="16"/>
       <c r="H34" s="16"/>
       <c r="I34" s="16" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="J34" s="16" t="s">
         <v>8</v>
@@ -4168,172 +4229,177 @@
       <c r="P34" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="Q34" s="36" t="s">
-        <v>179</v>
+      <c r="Q34" s="23" t="s">
+        <v>174</v>
       </c>
       <c r="R34" s="16"/>
-      <c r="S34" s="41"/>
+      <c r="S34" s="28"/>
       <c r="T34" s="17"/>
-    </row>
-    <row r="35" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="34" t="s">
-        <v>269</v>
-      </c>
-      <c r="B35" s="34" t="s">
-        <v>269</v>
-      </c>
-      <c r="C35" s="31" t="s">
+      <c r="U34" s="17"/>
+    </row>
+    <row r="35" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="C35" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="34" t="s">
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="J35" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18"/>
+      <c r="M35" s="21"/>
+      <c r="N35" s="21"/>
+      <c r="O35" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="P35" s="21"/>
+      <c r="Q35" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="R35" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="S35" s="29"/>
+      <c r="T35" s="21"/>
+      <c r="U35" s="21"/>
+    </row>
+    <row r="36" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="G36" s="21"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="21"/>
+      <c r="J36" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="K36" s="21"/>
+      <c r="L36" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="O36" s="21"/>
+      <c r="P36" s="21"/>
+      <c r="Q36" s="29"/>
+      <c r="R36" s="21"/>
+      <c r="S36" s="29"/>
+      <c r="T36" s="21"/>
+      <c r="U36" s="21"/>
+    </row>
+    <row r="37" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="24"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" s="25"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="G37" s="25"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="J37" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="K37" s="25"/>
+      <c r="L37" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="M37" s="24"/>
+      <c r="N37" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="O37" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="P37" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="Q37" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="J35" s="31" t="s">
-        <v>221</v>
-      </c>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="34"/>
-      <c r="N35" s="34"/>
-      <c r="O35" s="34" t="s">
-        <v>222</v>
-      </c>
-      <c r="P35" s="34"/>
-      <c r="Q35" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="R35" s="31" t="s">
-        <v>223</v>
-      </c>
-      <c r="S35" s="42"/>
-      <c r="T35" s="34"/>
-    </row>
-    <row r="36" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="34"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="31"/>
-      <c r="F36" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="K36" s="34"/>
-      <c r="L36" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="M36" s="31"/>
-      <c r="N36" s="31" t="s">
-        <v>98</v>
-      </c>
-      <c r="O36" s="34"/>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="42"/>
-      <c r="R36" s="34"/>
-      <c r="S36" s="42"/>
-      <c r="T36" s="34"/>
-    </row>
-    <row r="37" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="37"/>
-      <c r="B37" s="37"/>
-      <c r="C37" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38" t="s">
-        <v>224</v>
-      </c>
-      <c r="G37" s="38"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="J37" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="K37" s="38"/>
-      <c r="L37" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="M37" s="37"/>
-      <c r="N37" s="37" t="s">
-        <v>279</v>
-      </c>
-      <c r="O37" s="37" t="s">
-        <v>266</v>
-      </c>
-      <c r="P37" s="38" t="s">
-        <v>267</v>
-      </c>
-      <c r="Q37" s="39" t="s">
-        <v>178</v>
-      </c>
-      <c r="R37" s="38" t="s">
-        <v>220</v>
-      </c>
-      <c r="S37" s="40"/>
-      <c r="T37" s="38"/>
-    </row>
-    <row r="38" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="B38" s="34" t="s">
-        <v>303</v>
-      </c>
-      <c r="C38" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="D38" s="31"/>
-      <c r="E38" s="31" t="s">
+      <c r="R37" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="S37" s="27"/>
+      <c r="T37" s="25"/>
+      <c r="U37" s="25"/>
+    </row>
+    <row r="38" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="F38" s="31" t="s">
-        <v>165</v>
-      </c>
-      <c r="G38" s="31"/>
-      <c r="H38" s="31"/>
-      <c r="I38" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="J38" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="K38" s="31"/>
-      <c r="L38" s="31"/>
-      <c r="M38" s="31"/>
-      <c r="N38" s="31" t="s">
-        <v>264</v>
-      </c>
-      <c r="O38" s="31" t="s">
-        <v>314</v>
-      </c>
-      <c r="P38" s="31" t="s">
-        <v>315</v>
-      </c>
-      <c r="Q38" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="R38" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="S38" s="42"/>
-      <c r="T38" s="34"/>
-    </row>
-    <row r="39" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F38" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="G38" s="18"/>
+      <c r="H38" s="18"/>
+      <c r="I38" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="J38" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18"/>
+      <c r="N38" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="O38" s="18" t="s">
+        <v>308</v>
+      </c>
+      <c r="P38" s="18" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q38" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="R38" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="S38" s="29"/>
+      <c r="T38" s="21"/>
+      <c r="U38" s="21"/>
+    </row>
+    <row r="39" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="14"/>
       <c r="B39" s="14"/>
       <c r="C39" s="11" t="s">
@@ -4342,34 +4408,35 @@
       <c r="D39" s="11"/>
       <c r="E39" s="11"/>
       <c r="F39" s="11" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G39" s="11"/>
       <c r="H39" s="11"/>
       <c r="I39" s="14" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="K39" s="11"/>
       <c r="L39" s="11"/>
       <c r="M39" s="11"/>
       <c r="N39" s="11" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="O39" s="11" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="P39" s="14"/>
-      <c r="Q39" s="47"/>
+      <c r="Q39" s="34"/>
       <c r="R39" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="S39" s="47"/>
+        <v>106</v>
+      </c>
+      <c r="S39" s="34"/>
       <c r="T39" s="14"/>
-    </row>
-    <row r="40" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U39" s="14"/>
+    </row>
+    <row r="40" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="14"/>
       <c r="B40" s="14"/>
       <c r="C40" s="11" t="s">
@@ -4378,32 +4445,33 @@
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G40" s="11"/>
       <c r="H40" s="11"/>
       <c r="I40" s="14"/>
       <c r="J40" s="11" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="K40" s="11"/>
       <c r="L40" s="11"/>
       <c r="M40" s="14"/>
       <c r="N40" s="14" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="O40" s="14"/>
       <c r="P40" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="Q40" s="47"/>
+      <c r="Q40" s="34"/>
       <c r="R40" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="S40" s="47"/>
+        <v>207</v>
+      </c>
+      <c r="S40" s="34"/>
       <c r="T40" s="14"/>
-    </row>
-    <row r="41" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U40" s="14"/>
+    </row>
+    <row r="41" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="14"/>
       <c r="B41" s="14"/>
       <c r="C41" s="11" t="s">
@@ -4412,21 +4480,21 @@
       <c r="D41" s="11"/>
       <c r="E41" s="11"/>
       <c r="F41" s="11" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G41" s="11"/>
       <c r="H41" s="11"/>
       <c r="I41" s="14" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="K41" s="11"/>
       <c r="L41" s="11"/>
       <c r="M41" s="14"/>
       <c r="N41" s="14" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="O41" s="14" t="s">
         <v>18</v>
@@ -4434,14 +4502,15 @@
       <c r="P41" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="Q41" s="47"/>
+      <c r="Q41" s="34"/>
       <c r="R41" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="S41" s="47"/>
+        <v>89</v>
+      </c>
+      <c r="S41" s="34"/>
       <c r="T41" s="14"/>
-    </row>
-    <row r="42" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U41" s="14"/>
+    </row>
+    <row r="42" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="14"/>
       <c r="B42" s="14"/>
       <c r="C42" s="11" t="s">
@@ -4450,32 +4519,33 @@
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="G42" s="11"/>
       <c r="H42" s="11"/>
       <c r="I42" s="14" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="J42" s="11" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="K42" s="11"/>
       <c r="L42" s="11"/>
       <c r="M42" s="11"/>
       <c r="N42" s="11" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="O42" s="14"/>
       <c r="P42" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q42" s="47"/>
+        <v>202</v>
+      </c>
+      <c r="Q42" s="34"/>
       <c r="R42" s="11"/>
-      <c r="S42" s="47"/>
+      <c r="S42" s="34"/>
       <c r="T42" s="14"/>
-    </row>
-    <row r="43" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U42" s="14"/>
+    </row>
+    <row r="43" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="14"/>
       <c r="B43" s="14"/>
       <c r="C43" s="11" t="s">
@@ -4484,34 +4554,35 @@
       <c r="D43" s="11"/>
       <c r="E43" s="11"/>
       <c r="F43" s="11" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="G43" s="11"/>
       <c r="H43" s="11"/>
       <c r="I43" s="14"/>
       <c r="J43" s="11" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="K43" s="11"/>
       <c r="L43" s="11"/>
       <c r="M43" s="11"/>
       <c r="N43" s="11" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="O43" s="14" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="P43" s="14"/>
-      <c r="Q43" s="47"/>
+      <c r="Q43" s="34"/>
       <c r="R43" s="11"/>
-      <c r="S43" s="47"/>
+      <c r="S43" s="34"/>
       <c r="T43" s="14"/>
-    </row>
-    <row r="44" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U43" s="14"/>
+    </row>
+    <row r="44" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="14"/>
       <c r="B44" s="14"/>
       <c r="C44" s="11" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D44" s="11"/>
       <c r="E44" s="11"/>
@@ -4522,7 +4593,7 @@
       <c r="H44" s="11"/>
       <c r="I44" s="14"/>
       <c r="J44" s="11" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="K44" s="11"/>
       <c r="L44" s="11"/>
@@ -4532,14 +4603,15 @@
         <v>18</v>
       </c>
       <c r="P44" s="11" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="Q44" s="14"/>
       <c r="R44" s="11"/>
-      <c r="S44" s="47"/>
+      <c r="S44" s="34"/>
       <c r="T44" s="14"/>
-    </row>
-    <row r="45" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U44" s="14"/>
+    </row>
+    <row r="45" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="8"/>
       <c r="B45" s="8"/>
       <c r="C45" s="9" t="s">
@@ -4548,30 +4620,31 @@
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G45" s="9"/>
       <c r="H45" s="9"/>
       <c r="I45" s="8"/>
       <c r="J45" s="9" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
       <c r="M45" s="8"/>
       <c r="N45" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="O45" s="8" t="s">
         <v>18</v>
       </c>
       <c r="P45" s="8"/>
-      <c r="Q45" s="49"/>
+      <c r="Q45" s="36"/>
       <c r="R45" s="11"/>
-      <c r="S45" s="47"/>
+      <c r="S45" s="34"/>
       <c r="T45" s="14"/>
-    </row>
-    <row r="46" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U45" s="14"/>
+    </row>
+    <row r="46" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="8"/>
       <c r="B46" s="8"/>
       <c r="C46" s="9" t="s">
@@ -4580,19 +4653,19 @@
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G46" s="9"/>
       <c r="H46" s="9"/>
       <c r="I46" s="8"/>
       <c r="J46" s="9" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="K46" s="9"/>
       <c r="L46" s="9"/>
       <c r="M46" s="8"/>
       <c r="N46" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="O46" s="8" t="s">
         <v>18</v>
@@ -4600,12 +4673,13 @@
       <c r="P46" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="Q46" s="49"/>
+      <c r="Q46" s="36"/>
       <c r="R46" s="11"/>
-      <c r="S46" s="47"/>
+      <c r="S46" s="34"/>
       <c r="T46" s="14"/>
-    </row>
-    <row r="47" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U46" s="14"/>
+    </row>
+    <row r="47" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8"/>
       <c r="B47" s="8"/>
       <c r="C47" s="9" t="s">
@@ -4614,34 +4688,35 @@
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G47" s="9"/>
       <c r="H47" s="9"/>
       <c r="I47" s="9" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="K47" s="9"/>
       <c r="L47" s="9"/>
       <c r="M47" s="9"/>
       <c r="N47" s="9" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="P47" s="8"/>
-      <c r="Q47" s="50"/>
+      <c r="Q47" s="37"/>
       <c r="R47" s="11" t="s">
-        <v>111</v>
-      </c>
-      <c r="S47" s="47"/>
+        <v>106</v>
+      </c>
+      <c r="S47" s="34"/>
       <c r="T47" s="14"/>
-    </row>
-    <row r="48" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U47" s="14"/>
+    </row>
+    <row r="48" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8"/>
       <c r="B48" s="8"/>
       <c r="C48" s="9" t="s">
@@ -4650,32 +4725,33 @@
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G48" s="9"/>
       <c r="H48" s="9"/>
       <c r="I48" s="8"/>
       <c r="J48" s="9" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="K48" s="9"/>
       <c r="L48" s="9"/>
       <c r="M48" s="8"/>
       <c r="N48" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="O48" s="8" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="P48" s="8"/>
-      <c r="Q48" s="49"/>
+      <c r="Q48" s="36"/>
       <c r="R48" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="S48" s="47"/>
+        <v>234</v>
+      </c>
+      <c r="S48" s="34"/>
       <c r="T48" s="14"/>
-    </row>
-    <row r="49" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U48" s="14"/>
+    </row>
+    <row r="49" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="8"/>
       <c r="B49" s="8"/>
       <c r="C49" s="9" t="s">
@@ -4684,32 +4760,33 @@
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G49" s="9"/>
       <c r="H49" s="9"/>
       <c r="I49" s="8"/>
       <c r="J49" s="9" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="K49" s="9"/>
       <c r="L49" s="9"/>
       <c r="M49" s="8"/>
       <c r="N49" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="O49" s="8" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="P49" s="8"/>
-      <c r="Q49" s="49"/>
+      <c r="Q49" s="36"/>
       <c r="R49" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="S49" s="47"/>
+        <v>234</v>
+      </c>
+      <c r="S49" s="34"/>
       <c r="T49" s="14"/>
-    </row>
-    <row r="50" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U49" s="14"/>
+    </row>
+    <row r="50" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8"/>
       <c r="B50" s="8"/>
       <c r="C50" s="9" t="s">
@@ -4718,32 +4795,33 @@
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G50" s="9"/>
       <c r="H50" s="9"/>
       <c r="I50" s="8"/>
       <c r="J50" s="9" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="K50" s="9"/>
       <c r="L50" s="9"/>
       <c r="M50" s="8"/>
       <c r="N50" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="O50" s="8" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="P50" s="8"/>
-      <c r="Q50" s="49"/>
+      <c r="Q50" s="36"/>
       <c r="R50" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="S50" s="47"/>
+        <v>234</v>
+      </c>
+      <c r="S50" s="34"/>
       <c r="T50" s="14"/>
-    </row>
-    <row r="51" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U50" s="14"/>
+    </row>
+    <row r="51" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8"/>
       <c r="B51" s="8"/>
       <c r="C51" s="9" t="s">
@@ -4752,68 +4830,70 @@
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G51" s="9"/>
       <c r="H51" s="9"/>
       <c r="I51" s="8"/>
       <c r="J51" s="9" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="K51" s="9"/>
       <c r="L51" s="9"/>
       <c r="M51" s="8"/>
       <c r="N51" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="O51" s="8" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="P51" s="8"/>
-      <c r="Q51" s="49"/>
+      <c r="Q51" s="36"/>
       <c r="R51" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="S51" s="47"/>
+        <v>234</v>
+      </c>
+      <c r="S51" s="34"/>
       <c r="T51" s="14"/>
-    </row>
-    <row r="52" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="51"/>
-      <c r="B52" s="51"/>
-      <c r="C52" s="52" t="s">
+      <c r="U51" s="14"/>
+    </row>
+    <row r="52" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="38"/>
+      <c r="B52" s="38"/>
+      <c r="C52" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="D52" s="52"/>
-      <c r="E52" s="52"/>
-      <c r="F52" s="52" t="s">
-        <v>217</v>
-      </c>
-      <c r="G52" s="52"/>
-      <c r="H52" s="52"/>
-      <c r="I52" s="51"/>
-      <c r="J52" s="52" t="s">
-        <v>240</v>
-      </c>
-      <c r="K52" s="52"/>
-      <c r="L52" s="52" t="s">
+      <c r="D52" s="39"/>
+      <c r="E52" s="39"/>
+      <c r="F52" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="G52" s="39"/>
+      <c r="H52" s="39"/>
+      <c r="I52" s="38"/>
+      <c r="J52" s="39" t="s">
+        <v>235</v>
+      </c>
+      <c r="K52" s="39"/>
+      <c r="L52" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="M52" s="51"/>
-      <c r="N52" s="51" t="s">
-        <v>179</v>
-      </c>
-      <c r="O52" s="52" t="s">
-        <v>241</v>
-      </c>
-      <c r="P52" s="51"/>
-      <c r="Q52" s="53"/>
+      <c r="M52" s="38"/>
+      <c r="N52" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="O52" s="39" t="s">
+        <v>236</v>
+      </c>
+      <c r="P52" s="38"/>
+      <c r="Q52" s="40"/>
       <c r="R52" s="17" t="s">
-        <v>239</v>
-      </c>
-      <c r="S52" s="41"/>
+        <v>234</v>
+      </c>
+      <c r="S52" s="28"/>
       <c r="T52" s="17"/>
-    </row>
-    <row r="53" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U52" s="17"/>
+    </row>
+    <row r="53" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="9" t="s">
@@ -4822,141 +4902,145 @@
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G53" s="9"/>
       <c r="H53" s="9"/>
       <c r="I53" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="K53" s="9"/>
       <c r="L53" s="9"/>
       <c r="M53" s="9"/>
       <c r="N53" s="9" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="O53" s="8" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="P53" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q53" s="49"/>
+        <v>252</v>
+      </c>
+      <c r="Q53" s="36"/>
       <c r="R53" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="S53" s="47"/>
+        <v>89</v>
+      </c>
+      <c r="S53" s="34"/>
       <c r="T53" s="14"/>
-    </row>
-    <row r="54" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U53" s="14"/>
+    </row>
+    <row r="54" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8"/>
       <c r="B54" s="8"/>
       <c r="C54" s="9" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G54" s="9"/>
       <c r="H54" s="9"/>
       <c r="I54" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="K54" s="9"/>
       <c r="L54" s="9"/>
       <c r="M54" s="8"/>
       <c r="N54" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="O54" s="9" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="P54" s="8"/>
-      <c r="Q54" s="49"/>
-      <c r="R54" s="59" t="s">
-        <v>239</v>
+      <c r="Q54" s="36"/>
+      <c r="R54" s="45" t="s">
+        <v>234</v>
       </c>
       <c r="T54" s="14"/>
-    </row>
-    <row r="55" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U54" s="14"/>
+    </row>
+    <row r="55" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="8"/>
       <c r="B55" s="8"/>
       <c r="C55" s="9" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
       <c r="F55" s="9" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G55" s="9"/>
       <c r="H55" s="9"/>
       <c r="I55" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="K55" s="9"/>
       <c r="L55" s="9"/>
       <c r="M55" s="8"/>
       <c r="N55" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="P55" s="8"/>
-      <c r="Q55" s="49"/>
-      <c r="R55" s="50" t="s">
-        <v>239</v>
+      <c r="Q55" s="36"/>
+      <c r="R55" s="37" t="s">
+        <v>234</v>
       </c>
       <c r="T55" s="14"/>
-    </row>
-    <row r="56" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U55" s="14"/>
+    </row>
+    <row r="56" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8"/>
       <c r="B56" s="8"/>
       <c r="C56" s="9" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G56" s="9"/>
       <c r="H56" s="9"/>
       <c r="I56" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="K56" s="9"/>
       <c r="L56" s="9"/>
       <c r="M56" s="8"/>
       <c r="N56" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="O56" s="9" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="P56" s="8"/>
-      <c r="Q56" s="49"/>
-      <c r="R56" s="50" t="s">
-        <v>239</v>
+      <c r="Q56" s="36"/>
+      <c r="R56" s="37" t="s">
+        <v>234</v>
       </c>
       <c r="T56" s="14"/>
-    </row>
-    <row r="57" spans="1:20" s="33" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U56" s="14"/>
+    </row>
+    <row r="57" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="8"/>
       <c r="B57" s="8"/>
       <c r="C57" s="9" t="s">
@@ -4965,31 +5049,32 @@
       <c r="D57" s="9"/>
       <c r="E57" s="9"/>
       <c r="F57" s="9" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G57" s="9"/>
       <c r="H57" s="9"/>
       <c r="I57" s="8" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="K57" s="9"/>
       <c r="L57" s="9"/>
       <c r="M57" s="8"/>
       <c r="N57" s="8" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="P57" s="8"/>
-      <c r="Q57" s="49"/>
-      <c r="R57" s="50" t="s">
-        <v>239</v>
+      <c r="Q57" s="36"/>
+      <c r="R57" s="37" t="s">
+        <v>234</v>
       </c>
       <c r="T57" s="14"/>
+      <c r="U57" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5111,14 +5196,14 @@
         <v>62</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="27"/>
+      <c r="B3" s="56"/>
       <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
@@ -5129,10 +5214,10 @@
         <v>55</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>48</v>
@@ -5149,8 +5234,8 @@
       <c r="P3" s="3"/>
     </row>
     <row r="4" spans="1:16" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="22"/>
-      <c r="B4" s="28"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="57"/>
       <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
@@ -5161,10 +5246,10 @@
         <v>55</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>48</v>
@@ -5183,8 +5268,8 @@
       <c r="P4" s="3"/>
     </row>
     <row r="5" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="23"/>
-      <c r="B5" s="29"/>
+      <c r="A5" s="52"/>
+      <c r="B5" s="58"/>
       <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
@@ -5195,10 +5280,10 @@
         <v>55</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>57</v>
@@ -5217,10 +5302,10 @@
       <c r="P5" s="3"/>
     </row>
     <row r="6" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="47" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -5233,10 +5318,10 @@
         <v>55</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="G6" s="18" t="s">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="G6" s="47" t="s">
+        <v>91</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>47</v>
@@ -5255,8 +5340,8 @@
       <c r="P6" s="3"/>
     </row>
     <row r="7" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="25"/>
-      <c r="B7" s="19"/>
+      <c r="A7" s="54"/>
+      <c r="B7" s="48"/>
       <c r="C7" s="3" t="s">
         <v>10</v>
       </c>
@@ -5267,9 +5352,9 @@
         <v>55</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G7" s="19"/>
+        <v>93</v>
+      </c>
+      <c r="G7" s="48"/>
       <c r="H7" s="4" t="s">
         <v>48</v>
       </c>
@@ -5287,8 +5372,8 @@
       <c r="P7" s="3"/>
     </row>
     <row r="8" spans="1:16" ht="150" x14ac:dyDescent="0.25">
-      <c r="A8" s="25"/>
-      <c r="B8" s="19"/>
+      <c r="A8" s="54"/>
+      <c r="B8" s="48"/>
       <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
@@ -5299,9 +5384,9 @@
         <v>55</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="G8" s="19"/>
+        <v>90</v>
+      </c>
+      <c r="G8" s="48"/>
       <c r="H8" s="4" t="s">
         <v>50</v>
       </c>
@@ -5319,8 +5404,8 @@
       <c r="P8" s="3"/>
     </row>
     <row r="9" spans="1:16" ht="75" x14ac:dyDescent="0.25">
-      <c r="A9" s="25"/>
-      <c r="B9" s="19"/>
+      <c r="A9" s="54"/>
+      <c r="B9" s="48"/>
       <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
@@ -5331,7 +5416,7 @@
         <v>55</v>
       </c>
       <c r="F9" s="4"/>
-      <c r="G9" s="19"/>
+      <c r="G9" s="48"/>
       <c r="H9" s="4" t="s">
         <v>50</v>
       </c>
@@ -5349,8 +5434,8 @@
       <c r="P9" s="3"/>
     </row>
     <row r="10" spans="1:16" ht="75" x14ac:dyDescent="0.25">
-      <c r="A10" s="25"/>
-      <c r="B10" s="19"/>
+      <c r="A10" s="54"/>
+      <c r="B10" s="48"/>
       <c r="C10" s="3" t="s">
         <v>12</v>
       </c>
@@ -5361,9 +5446,9 @@
         <v>55</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="G10" s="19"/>
+        <v>93</v>
+      </c>
+      <c r="G10" s="48"/>
       <c r="H10" s="4" t="s">
         <v>50</v>
       </c>
@@ -5381,8 +5466,8 @@
       <c r="P10" s="3"/>
     </row>
     <row r="11" spans="1:16" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="26"/>
-      <c r="B11" s="20"/>
+      <c r="A11" s="55"/>
+      <c r="B11" s="49"/>
       <c r="C11" s="3" t="s">
         <v>13</v>
       </c>
@@ -5393,9 +5478,9 @@
         <v>55</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="G11" s="20"/>
+        <v>92</v>
+      </c>
+      <c r="G11" s="49"/>
       <c r="H11" s="4" t="s">
         <v>48</v>
       </c>
@@ -5413,10 +5498,10 @@
       <c r="P11" s="3"/>
     </row>
     <row r="12" spans="1:16" ht="60" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="27"/>
+      <c r="B12" s="56"/>
       <c r="C12" s="3" t="s">
         <v>14</v>
       </c>
@@ -5449,8 +5534,8 @@
       <c r="P12" s="3"/>
     </row>
     <row r="13" spans="1:16" ht="90" x14ac:dyDescent="0.25">
-      <c r="A13" s="20"/>
-      <c r="B13" s="29"/>
+      <c r="A13" s="49"/>
+      <c r="B13" s="58"/>
       <c r="C13" s="3" t="s">
         <v>16</v>
       </c>
@@ -5461,7 +5546,7 @@
         <v>55</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="4" t="s">
@@ -5537,7 +5622,7 @@
         <v>73</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>19</v>
@@ -5546,10 +5631,10 @@
         <v>54</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>56</v>
@@ -5587,26 +5672,26 @@
     </row>
     <row r="2" spans="1:18" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="13" t="s">
-        <v>108</v>
-      </c>
       <c r="C2" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="D2" s="9" t="s">
-        <v>129</v>
-      </c>
       <c r="E2" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="4" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
@@ -5620,110 +5705,110 @@
       <c r="R2" s="3"/>
     </row>
     <row r="3" spans="1:18" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>107</v>
+      <c r="B3" s="47" t="s">
+        <v>102</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>151</v>
+        <v>125</v>
+      </c>
+      <c r="F3" s="47" t="s">
+        <v>145</v>
+      </c>
+      <c r="G3" s="47" t="s">
+        <v>146</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="4" t="s">
         <v>48</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="L3" s="4"/>
       <c r="M3" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
       <c r="Q3" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="R3" s="3"/>
     </row>
     <row r="4" spans="1:18" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
+      <c r="A4" s="48"/>
+      <c r="B4" s="48"/>
       <c r="C4" s="4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
+        <v>125</v>
+      </c>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="4" t="s">
         <v>48</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="L4" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="M4" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="M4" s="4" t="s">
-        <v>138</v>
-      </c>
       <c r="N4" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="R4" s="3"/>
     </row>
     <row r="5" spans="1:18" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20"/>
-      <c r="B5" s="20"/>
+      <c r="A5" s="49"/>
+      <c r="B5" s="49"/>
       <c r="C5" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
       <c r="H5" s="3" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -5734,20 +5819,20 @@
       <c r="R5" s="3"/>
     </row>
     <row r="6" spans="1:18" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="59" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="59" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="30" t="s">
-        <v>109</v>
-      </c>
       <c r="C6" s="4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
@@ -5757,7 +5842,7 @@
         <v>47</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -5765,21 +5850,21 @@
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
       <c r="Q6" s="3" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="R6" s="3"/>
     </row>
     <row r="7" spans="1:18" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="30"/>
-      <c r="B7" s="30"/>
+      <c r="A7" s="59"/>
+      <c r="B7" s="59"/>
       <c r="C7" s="4" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
@@ -5796,16 +5881,16 @@
       <c r="R7" s="3"/>
     </row>
     <row r="8" spans="1:18" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
-      <c r="B8" s="30"/>
+      <c r="A8" s="59"/>
+      <c r="B8" s="59"/>
       <c r="C8" s="4" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
@@ -5819,31 +5904,31 @@
       <c r="O8" s="3"/>
       <c r="P8" s="3"/>
       <c r="Q8" s="4" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="R8" s="3"/>
     </row>
     <row r="9" spans="1:18" ht="105" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="30"/>
+      <c r="A9" s="59"/>
+      <c r="B9" s="59"/>
       <c r="C9" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="F9" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
       <c r="K9" s="4" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
@@ -5854,39 +5939,39 @@
       <c r="R9" s="3"/>
     </row>
     <row r="10" spans="1:18" ht="105" x14ac:dyDescent="0.25">
-      <c r="A10" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>116</v>
+      <c r="A10" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="47" t="s">
+        <v>111</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="4" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
@@ -5894,30 +5979,30 @@
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:18" ht="105" x14ac:dyDescent="0.25">
-      <c r="A11" s="25"/>
-      <c r="B11" s="19"/>
+      <c r="A11" s="54"/>
+      <c r="B11" s="48"/>
       <c r="C11" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="K11" s="4" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -5928,25 +6013,25 @@
       <c r="R11" s="3"/>
     </row>
     <row r="12" spans="1:18" ht="105" x14ac:dyDescent="0.25">
-      <c r="A12" s="26"/>
-      <c r="B12" s="20"/>
+      <c r="A12" s="55"/>
+      <c r="B12" s="49"/>
       <c r="C12" s="3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
@@ -5961,7 +6046,7 @@
     </row>
     <row r="13" spans="1:18" ht="105" x14ac:dyDescent="0.25">
       <c r="F13" s="2" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -6010,7 +6095,7 @@
         <v>73</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>19</v>
@@ -6019,10 +6104,10 @@
         <v>54</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>56</v>
@@ -6060,32 +6145,32 @@
     </row>
     <row r="2" spans="1:18" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>108</v>
-      </c>
       <c r="C2" s="11" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E2" s="14" t="s">
         <v>55</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="G2" s="18" t="s">
-        <v>201</v>
+        <v>182</v>
+      </c>
+      <c r="G2" s="47" t="s">
+        <v>196</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>18</v>
@@ -6098,7 +6183,7 @@
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
       <c r="Q2" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="R2" s="3"/>
     </row>
@@ -6107,23 +6192,23 @@
         <v>4</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>55</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="G3" s="25"/>
+        <v>184</v>
+      </c>
+      <c r="G3" s="54"/>
       <c r="H3" s="12" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" s="12" t="s">
@@ -6138,35 +6223,35 @@
       <c r="O3" s="7"/>
       <c r="P3" s="7"/>
       <c r="Q3" s="7" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="R3" s="7"/>
     </row>
     <row r="4" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="G4" s="25"/>
+        <v>189</v>
+      </c>
+      <c r="G4" s="54"/>
       <c r="H4" s="11" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>47</v>
@@ -6175,39 +6260,39 @@
         <v>18</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="3" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="R4" s="3"/>
     </row>
     <row r="5" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>55</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="G5" s="26"/>
+        <v>195</v>
+      </c>
+      <c r="G5" s="55"/>
       <c r="H5" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
@@ -6222,7 +6307,7 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="R5" s="3"/>
     </row>
@@ -6246,10 +6331,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
@@ -6260,7 +6345,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C2" s="3"/>
     </row>
@@ -6269,10 +6354,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -6293,89 +6378,54 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>84</v>
-      </c>
       <c r="D1" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>80</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>85</v>
       </c>
       <c r="D2" s="10"/>
     </row>
     <row r="3" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D3" s="10"/>
     </row>
     <row r="4" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC3B9A8F-BA65-4659-A5BD-1079A87FFF80}">
-  <dimension ref="A2:A6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/Auxiliary resources/MMCI Literature review matrices.xlsx
+++ b/Auxiliary resources/MMCI Literature review matrices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\Dissertation\Auxiliary resources\Matrix literature review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1CC8BBD-3871-4A58-9F96-35FD0DC9FB5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B422F14-905E-479F-8F78-EC537CDD9393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1EA815CA-3631-4EEA-BC35-EAE153F95668}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="876" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="387">
   <si>
     <t>Dimension</t>
   </si>
@@ -825,9 +825,6 @@
     <t>A focus on adaption suggests that human modifications to the environmental, can, when succesfull, reduce vulnerability and thus enhance staying capability. It may include irrigation systems, flood control infraestructure, land restoration, and marine protected areas</t>
   </si>
   <si>
-    <t>Chronic illness</t>
-  </si>
-  <si>
     <t>Affects capability to migrate negatively</t>
   </si>
   <si>
@@ -862,9 +859,6 @@
   </si>
   <si>
     <t>Being able to hold property</t>
-  </si>
-  <si>
-    <t>Adequate Shelter</t>
   </si>
   <si>
     <t>Obi index</t>
@@ -954,9 +948,6 @@
   </si>
   <si>
     <t>Not identified</t>
-  </si>
-  <si>
-    <t>Affect capability to migrate positively</t>
   </si>
   <si>
     <t>(B) Material. Being able to hold property (both land and movable
@@ -993,33 +984,15 @@
     <t>It can erode capacity to stay</t>
   </si>
   <si>
-    <t>MxFLS question</t>
-  </si>
-  <si>
     <t>MxFLS section</t>
   </si>
   <si>
     <t>AC01: Does this community organize activities, meetings or assemblies?</t>
   </si>
   <si>
-    <t>Number of cooperatives in the community</t>
-  </si>
-  <si>
-    <t>Nussbaum's capability domain</t>
-  </si>
-  <si>
     <t>CA determinant</t>
   </si>
   <si>
-    <t>D1_I1_V1</t>
-  </si>
-  <si>
-    <t>D1_I1_V2</t>
-  </si>
-  <si>
-    <t>D1_I2_V1</t>
-  </si>
-  <si>
     <t>Community characteristics - AS (Social Assistance)</t>
   </si>
   <si>
@@ -1105,9 +1078,6 @@
   </si>
   <si>
     <t>ES08: Did you have a permanent injury that changed your way of living due to the accident?</t>
-  </si>
-  <si>
-    <t>Disability</t>
   </si>
   <si>
     <t>Comparative health status (self assessment)</t>
@@ -1150,23 +1120,12 @@
     <t>ECType: EC01: Have you ever been diagnosed with (….)?</t>
   </si>
   <si>
-    <t>What remains to be done</t>
-  </si>
-  <si>
-    <t>1. I need to calculate percentages for those that reported the quantitity
-2. I need to do the calculation in an individual level dataset
-3. I need to join the datasets and replace</t>
-  </si>
-  <si>
     <t>Community meeting</t>
   </si>
   <si>
     <t>Community meetings</t>
   </si>
   <si>
-    <t>The community organizes meetings</t>
-  </si>
-  <si>
     <t>Activate population attendance to community meetings</t>
   </si>
   <si>
@@ -1177,6 +1136,93 @@
   </si>
   <si>
     <t>No, the variable has many outliers, and people who did not report well</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The community organizes meetings </t>
+  </si>
+  <si>
+    <t>MxFLS possible question 1</t>
+  </si>
+  <si>
+    <t>MxFLS possible question 2</t>
+  </si>
+  <si>
+    <t>The variable is reported consistently. In wave II and III data must be consolidated</t>
+  </si>
+  <si>
+    <t>AC01a: Provides description of the types of activities (political, social, religious), but it is only available for wave II and III</t>
+  </si>
+  <si>
+    <t>1. Book C - Control Book</t>
+  </si>
+  <si>
+    <t>CVO-Direct Observation of Dwelling Characteristics (multiple)</t>
+  </si>
+  <si>
+    <t>Nussbaum's capability domain2</t>
+  </si>
+  <si>
+    <t>Number2</t>
+  </si>
+  <si>
+    <t>State in STATA</t>
+  </si>
+  <si>
+    <t>Completed (panel created)</t>
+  </si>
+  <si>
+    <t>D1_V1_I1</t>
+  </si>
+  <si>
+    <t>D1_V1_I2</t>
+  </si>
+  <si>
+    <t>D1_V2_I1</t>
+  </si>
+  <si>
+    <t>Existence of cooperatives in the community</t>
+  </si>
+  <si>
+    <t>D1_V2_I2</t>
+  </si>
+  <si>
+    <t>Government support to cooperatives in community</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AS05: In the last 12 months, how many community cooperatives have received geverment (federal, municipality, state) subsidies? </t>
+  </si>
+  <si>
+    <t>Can enhance/erode both, the important is the interaction with other factors</t>
+  </si>
+  <si>
+    <t>D2_V1_I1_A</t>
+  </si>
+  <si>
+    <t>D2_V1_I1_B</t>
+  </si>
+  <si>
+    <t>Recent incidences that affect health status</t>
+  </si>
+  <si>
+    <t>D2_V2</t>
+  </si>
+  <si>
+    <t>D2_V3_1</t>
+  </si>
+  <si>
+    <t>Disability and life-constraining health problems</t>
+  </si>
+  <si>
+    <t>D2_V3_2</t>
+  </si>
+  <si>
+    <t>D2_V3_3</t>
+  </si>
+  <si>
+    <t>D2_V4</t>
+  </si>
+  <si>
+    <t>Protection from adequate Shelter</t>
   </si>
 </sst>
 </file>
@@ -1339,7 +1385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1399,9 +1445,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1420,22 +1463,10 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1456,19 +1487,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1510,23 +1535,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="26">
     <dxf>
       <font>
         <b val="0"/>
@@ -1708,6 +1727,39 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Garamond"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2144,6 +2196,39 @@
         <family val="1"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Garamond"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="left" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -2238,32 +2323,40 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{205A4EAD-79AC-46AE-89E1-8D7FFBE1AC1D}" name="Table1" displayName="Table1" ref="A1:U57" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22" tableBorderDxfId="21">
-  <autoFilter ref="A1:U57" xr:uid="{205A4EAD-79AC-46AE-89E1-8D7FFBE1AC1D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R57">
-    <sortCondition ref="A1:A57"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{205A4EAD-79AC-46AE-89E1-8D7FFBE1AC1D}" name="Table1" displayName="Table1" ref="A1:W58" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24" tableBorderDxfId="23">
+  <autoFilter ref="A1:W58" xr:uid="{205A4EAD-79AC-46AE-89E1-8D7FFBE1AC1D}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Bodiliy health"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T58">
+    <sortCondition ref="A1:A58"/>
   </sortState>
-  <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{CBA470E9-2761-4E7B-95D5-EEA3137A21A6}" name="Nussbaum's capability domain" dataDxfId="20"/>
-    <tableColumn id="18" xr3:uid="{E49D1BA9-45F5-4866-9FC1-8B7D65B132BA}" name="Nussbaum's definition" dataDxfId="19"/>
-    <tableColumn id="14" xr3:uid="{9668895B-6A1F-46C1-9CB4-4EF8EDF7ACA8}" name="CA determinant" dataDxfId="18"/>
-    <tableColumn id="8" xr3:uid="{C85D8B0B-226A-4471-92F2-09021F6BB258}" name="Number" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{642A1707-42F2-4967-B446-AE1AC8011EBD}" name="Level MxFLS" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{5D94FE2C-CAC7-41EC-9236-BB9F6A0EFF94}" name="Study level dimension (Obi/R-Peña/Hosnedlova)" dataDxfId="15"/>
-    <tableColumn id="22" xr3:uid="{F3488BEE-30B3-4F02-9BD8-6A5BEB8BA4AF}" name="Schewel's dimensions" dataDxfId="14"/>
-    <tableColumn id="20" xr3:uid="{64ACCA7A-3E62-4C90-97FC-599C0A211D65}" name="Author" dataDxfId="13"/>
-    <tableColumn id="21" xr3:uid="{331ACB1B-F439-4A5A-95A8-F01B7FC11CB3}" name="Reference" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{9F13372D-BE7C-43DA-B27F-7E69A7AD803E}" name="Variable" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{82C2EF7E-7626-4535-AFEC-2650F35F7DB9}" name="Indicator" dataDxfId="10"/>
-    <tableColumn id="15" xr3:uid="{A9D86E20-5A8B-40AA-B391-65B5FD99ED4D}" name="Question (original author)" dataDxfId="9"/>
-    <tableColumn id="13" xr3:uid="{48D319ED-3810-41A9-AF63-BA4BF4E027F2}" name="MxFLS section" dataDxfId="8"/>
-    <tableColumn id="16" xr3:uid="{2AB760BD-7C92-4F25-AF7A-E2A52BFDE1FB}" name="MxFLS question" dataDxfId="7"/>
+  <tableColumns count="23">
+    <tableColumn id="1" xr3:uid="{CBA470E9-2761-4E7B-95D5-EEA3137A21A6}" name="Number" dataDxfId="22"/>
+    <tableColumn id="9" xr3:uid="{FB80F726-F99A-4E15-A0DA-9502576FEEA5}" name="Nussbaum's capability domain2" dataDxfId="21"/>
+    <tableColumn id="18" xr3:uid="{E49D1BA9-45F5-4866-9FC1-8B7D65B132BA}" name="Nussbaum's definition" dataDxfId="20"/>
+    <tableColumn id="14" xr3:uid="{9668895B-6A1F-46C1-9CB4-4EF8EDF7ACA8}" name="CA determinant" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{C85D8B0B-226A-4471-92F2-09021F6BB258}" name="Number2" dataDxfId="18"/>
+    <tableColumn id="12" xr3:uid="{642A1707-42F2-4967-B446-AE1AC8011EBD}" name="Level MxFLS" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{5D94FE2C-CAC7-41EC-9236-BB9F6A0EFF94}" name="Study level dimension (Obi/R-Peña/Hosnedlova)" dataDxfId="16"/>
+    <tableColumn id="22" xr3:uid="{F3488BEE-30B3-4F02-9BD8-6A5BEB8BA4AF}" name="Schewel's dimensions" dataDxfId="15"/>
+    <tableColumn id="20" xr3:uid="{64ACCA7A-3E62-4C90-97FC-599C0A211D65}" name="Author" dataDxfId="14"/>
+    <tableColumn id="21" xr3:uid="{331ACB1B-F439-4A5A-95A8-F01B7FC11CB3}" name="Reference" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{9F13372D-BE7C-43DA-B27F-7E69A7AD803E}" name="Variable" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{82C2EF7E-7626-4535-AFEC-2650F35F7DB9}" name="Indicator" dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{A9D86E20-5A8B-40AA-B391-65B5FD99ED4D}" name="Question (original author)" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{48D319ED-3810-41A9-AF63-BA4BF4E027F2}" name="MxFLS section" dataDxfId="9"/>
+    <tableColumn id="16" xr3:uid="{2AB760BD-7C92-4F25-AF7A-E2A52BFDE1FB}" name="MxFLS possible question 1" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{259A1B5A-677B-44EC-9E40-5FA26A570862}" name="MxFLS possible question 2" dataDxfId="7"/>
     <tableColumn id="6" xr3:uid="{0C3128B9-5B21-45D0-AC3E-898982331141}" name="Capability to stay" dataDxfId="6"/>
     <tableColumn id="7" xr3:uid="{2B387827-DEAE-4AA7-8AF0-103E8EC5EB2C}" name="Capabiltiy to leave" dataDxfId="5"/>
     <tableColumn id="17" xr3:uid="{05332881-CA52-42D3-B038-B13CB02B4F0F}" name="Incorporation decision" dataDxfId="4"/>
     <tableColumn id="11" xr3:uid="{06CB4C1D-8C05-4D74-9D76-48F61FE2E8A2}" name="Incorporation rule" dataDxfId="3"/>
     <tableColumn id="23" xr3:uid="{6A38D615-E512-4599-8142-55B257B60373}" name="Cleaning in STATA" dataDxfId="2"/>
-    <tableColumn id="25" xr3:uid="{62C0414C-0F32-4965-9B86-352FF82B351F}" name="What remains to be done" dataDxfId="1"/>
+    <tableColumn id="25" xr3:uid="{62C0414C-0F32-4965-9B86-352FF82B351F}" name="State in STATA" dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{42958CCE-6D89-442E-AA0F-AE71D7632606}" name="Decision after cleaning in STATA" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -2587,2494 +2680,2842 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53C6D3BA-C091-4098-987E-D59F3E361AAB}">
-  <dimension ref="A1:U57"/>
+  <dimension ref="A1:W58"/>
   <sheetFormatPr defaultRowHeight="50.1" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.140625" style="20" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" style="20" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="33" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" style="33" customWidth="1"/>
-    <col min="5" max="5" width="13" style="33" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" style="33" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="33" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" style="33" customWidth="1"/>
-    <col min="9" max="9" width="17" style="33" customWidth="1"/>
-    <col min="10" max="10" width="20" style="33" customWidth="1"/>
-    <col min="11" max="13" width="27.28515625" style="33" customWidth="1"/>
-    <col min="14" max="14" width="34.140625" style="33" customWidth="1"/>
-    <col min="15" max="15" width="29.28515625" style="20" customWidth="1"/>
-    <col min="16" max="16" width="21.85546875" style="20" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="20" customWidth="1"/>
-    <col min="18" max="18" width="23.140625" style="33" customWidth="1"/>
-    <col min="19" max="19" width="16.5703125" style="20" customWidth="1"/>
-    <col min="20" max="20" width="35" style="20" customWidth="1"/>
-    <col min="21" max="21" width="19.5703125" style="20" customWidth="1"/>
-    <col min="22" max="22" width="9.140625" style="20" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="20"/>
+    <col min="1" max="2" width="15.140625" style="20" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" style="20" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" style="29" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" style="29" customWidth="1"/>
+    <col min="6" max="6" width="13" style="29" customWidth="1"/>
+    <col min="7" max="7" width="21.85546875" style="29" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="29" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" style="29" customWidth="1"/>
+    <col min="10" max="10" width="17" style="29" customWidth="1"/>
+    <col min="11" max="11" width="20" style="29" customWidth="1"/>
+    <col min="12" max="14" width="27.28515625" style="29" customWidth="1"/>
+    <col min="15" max="16" width="34.140625" style="29" customWidth="1"/>
+    <col min="17" max="17" width="29.28515625" style="20" customWidth="1"/>
+    <col min="18" max="18" width="21.85546875" style="20" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="20" customWidth="1"/>
+    <col min="20" max="20" width="23.140625" style="29" customWidth="1"/>
+    <col min="21" max="21" width="16.5703125" style="20" customWidth="1"/>
+    <col min="22" max="22" width="35" style="20" customWidth="1"/>
+    <col min="23" max="23" width="19.5703125" style="20" customWidth="1"/>
+    <col min="24" max="24" width="9.140625" style="20" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>283</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>366</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="H1" s="19" t="s">
         <v>314</v>
       </c>
-      <c r="B1" s="41" t="s">
-        <v>285</v>
-      </c>
-      <c r="C1" s="19" t="s">
-        <v>315</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="E1" s="19" t="s">
-        <v>306</v>
-      </c>
-      <c r="F1" s="19" t="s">
+      <c r="I1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="K1" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="M1" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="N1" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="O1" s="19" t="s">
+        <v>359</v>
+      </c>
+      <c r="P1" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="Q1" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="R1" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="S1" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="T1" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="U1" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="V1" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="W1" s="19" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="21">
+        <v>1</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="J2" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>352</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="M2" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="N2" s="18" t="s">
+        <v>311</v>
+      </c>
+      <c r="O2" s="18" t="s">
+        <v>308</v>
+      </c>
+      <c r="P2" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="Q2" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="R2" s="21"/>
+      <c r="S2" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="T2" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="U2" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="V2" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="W2" s="18" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="38">
+        <v>2</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>265</v>
+      </c>
+      <c r="C3" s="38" t="s">
+        <v>286</v>
+      </c>
+      <c r="D3" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="F3" s="39" t="s">
+        <v>304</v>
+      </c>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="38" t="s">
+        <v>316</v>
+      </c>
+      <c r="J3" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="K3" s="39" t="s">
+        <v>353</v>
+      </c>
+      <c r="L3" s="39" t="s">
+        <v>354</v>
+      </c>
+      <c r="M3" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="N3" s="39" t="s">
+        <v>311</v>
+      </c>
+      <c r="O3" s="39" t="s">
+        <v>313</v>
+      </c>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="38"/>
+      <c r="S3" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="T3" s="39" t="s">
+        <v>357</v>
+      </c>
+      <c r="U3" s="38" t="s">
         <v>324</v>
       </c>
-      <c r="G1" s="19" t="s">
-        <v>323</v>
-      </c>
-      <c r="H1" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="I1" s="19" t="s">
+      <c r="V3" s="39"/>
+      <c r="W3" s="39" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21">
+        <v>3</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="J4" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="K4" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="L4" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="M4" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="N4" s="18" t="s">
+        <v>310</v>
+      </c>
+      <c r="O4" s="18" t="s">
+        <v>312</v>
+      </c>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="R4" s="21"/>
+      <c r="S4" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="T4" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="U4" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="V4" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="W4" s="21"/>
+    </row>
+    <row r="5" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="21">
+        <v>4</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="J5" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="K5" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="L5" s="18" t="s">
+        <v>374</v>
+      </c>
+      <c r="M5" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="N5" s="18" t="s">
+        <v>310</v>
+      </c>
+      <c r="O5" s="18" t="s">
+        <v>375</v>
+      </c>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="R5" s="21"/>
+      <c r="S5" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="T5" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="U5" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="V5" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="W5" s="21"/>
+    </row>
+    <row r="6" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="16">
+        <v>5</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="16"/>
+      <c r="I6" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="O6" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R6" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="S6" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="T6" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="U6" s="16" t="s">
         <v>326</v>
       </c>
-      <c r="J1" s="19" t="s">
-        <v>305</v>
-      </c>
-      <c r="K1" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="L1" s="19" t="s">
-        <v>271</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>311</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="O1" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="P1" s="19" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q1" s="19" t="s">
-        <v>273</v>
-      </c>
-      <c r="R1" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="S1" s="46" t="s">
+      <c r="V6" s="16"/>
+      <c r="W6" s="16"/>
+    </row>
+    <row r="7" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="16">
+        <v>6</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="16"/>
+      <c r="I7" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="M7" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="O7" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="P7" s="16"/>
+      <c r="Q7" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R7" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="S7" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="T7" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="U7" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="V7" s="16"/>
+      <c r="W7" s="16"/>
+    </row>
+    <row r="8" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="23">
+        <v>7</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="T8" s="24" t="s">
+        <v>349</v>
+      </c>
+      <c r="U8" s="23"/>
+      <c r="V8" s="23"/>
+      <c r="W8" s="23"/>
+    </row>
+    <row r="9" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="21">
+        <v>8</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="J9" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="M9" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="N9" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="O9" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="R9" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="S9" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="T9" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="U9" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="V9" s="21"/>
+      <c r="W9" s="21"/>
+    </row>
+    <row r="10" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>9</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="M10" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="N10" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="O10" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R10" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="S10" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="T10" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="U10" s="16"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
+    </row>
+    <row r="11" spans="1:23" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="21">
+        <v>10</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18" t="s">
+        <v>316</v>
+      </c>
+      <c r="J11" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="K11" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="L11" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="T1" s="44" t="s">
-        <v>362</v>
-      </c>
-      <c r="U1" s="44" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="21" t="s">
-        <v>266</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="D2" s="18" t="s">
+      <c r="M11" s="18"/>
+      <c r="N11" s="18" t="s">
+        <v>329</v>
+      </c>
+      <c r="O11" s="18" t="s">
+        <v>334</v>
+      </c>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="R11" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="S11" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="T11" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="U11" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="V11" s="18"/>
+      <c r="W11" s="18"/>
+    </row>
+    <row r="12" spans="1:23" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="21">
+        <v>11</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>380</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18" t="s">
         <v>316</v>
       </c>
-      <c r="E2" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="21" t="s">
+      <c r="J12" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="K12" s="18" t="s">
+        <v>379</v>
+      </c>
+      <c r="L12" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18" t="s">
+        <v>329</v>
+      </c>
+      <c r="O12" s="18" t="s">
+        <v>333</v>
+      </c>
+      <c r="P12" s="18"/>
+      <c r="Q12" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="R12" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="S12" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="T12" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="U12" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="V12" s="18"/>
+      <c r="W12" s="18"/>
+    </row>
+    <row r="13" spans="1:23" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="21">
+        <v>12</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>378</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18" t="s">
+        <v>316</v>
+      </c>
+      <c r="J13" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="J2" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="K2" s="18" t="s">
-        <v>366</v>
-      </c>
-      <c r="L2" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="M2" s="18" t="s">
-        <v>320</v>
-      </c>
-      <c r="N2" s="18" t="s">
-        <v>312</v>
-      </c>
-      <c r="O2" s="18" t="s">
+      <c r="K13" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="L13" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18" t="s">
+        <v>329</v>
+      </c>
+      <c r="O13" s="18" t="s">
+        <v>335</v>
+      </c>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="R13" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="S13" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="T13" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="U13" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="V13" s="18"/>
+      <c r="W13" s="18"/>
+    </row>
+    <row r="14" spans="1:23" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="21">
+        <v>13</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>378</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18" t="s">
+        <v>316</v>
+      </c>
+      <c r="J14" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="K14" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="L14" s="18" t="s">
+        <v>339</v>
+      </c>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18" t="s">
+        <v>329</v>
+      </c>
+      <c r="O14" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="P14" s="18"/>
+      <c r="Q14" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="R14" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="S14" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="T14" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="U14" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="V14" s="18"/>
+      <c r="W14" s="18"/>
+    </row>
+    <row r="15" spans="1:23" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="21">
+        <v>14</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>381</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18" t="s">
+        <v>316</v>
+      </c>
+      <c r="J15" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="K15" s="18" t="s">
+        <v>382</v>
+      </c>
+      <c r="L15" s="18" t="s">
+        <v>337</v>
+      </c>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18" t="s">
+        <v>329</v>
+      </c>
+      <c r="O15" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="R15" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="S15" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="T15" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="U15" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="V15" s="18"/>
+      <c r="W15" s="18"/>
+    </row>
+    <row r="16" spans="1:23" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="23">
+        <v>15</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24" t="s">
+        <v>316</v>
+      </c>
+      <c r="J16" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>382</v>
+      </c>
+      <c r="L16" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24" t="s">
+        <v>329</v>
+      </c>
+      <c r="O16" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="24"/>
+      <c r="S16" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="T16" s="24" t="s">
+        <v>343</v>
+      </c>
+      <c r="U16" s="23"/>
+      <c r="V16" s="23"/>
+      <c r="W16" s="23"/>
+    </row>
+    <row r="17" spans="1:23" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="23">
+        <v>16</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="24" t="s">
+        <v>385</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24" t="s">
+        <v>316</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>344</v>
+      </c>
+      <c r="L17" s="24" t="s">
+        <v>345</v>
+      </c>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24" t="s">
+        <v>329</v>
+      </c>
+      <c r="O17" s="24" t="s">
+        <v>346</v>
+      </c>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="24"/>
+      <c r="S17" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="T17" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="U17" s="23"/>
+      <c r="V17" s="23"/>
+      <c r="W17" s="23"/>
+    </row>
+    <row r="18" spans="1:23" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="21">
+        <v>17</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="18" t="s">
+        <v>384</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18" t="s">
+        <v>316</v>
+      </c>
+      <c r="J18" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>382</v>
+      </c>
+      <c r="L18" s="18" t="s">
         <v>327</v>
-      </c>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="R2" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="S2" s="29" t="s">
-        <v>332</v>
-      </c>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-    </row>
-    <row r="3" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="60" t="s">
-        <v>266</v>
-      </c>
-      <c r="B3" s="60" t="s">
-        <v>288</v>
-      </c>
-      <c r="C3" s="61" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3" s="61" t="s">
-        <v>317</v>
-      </c>
-      <c r="E3" s="61" t="s">
-        <v>307</v>
-      </c>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="60" t="s">
-        <v>325</v>
-      </c>
-      <c r="I3" s="60" t="s">
-        <v>168</v>
-      </c>
-      <c r="J3" s="61" t="s">
-        <v>365</v>
-      </c>
-      <c r="K3" s="61" t="s">
-        <v>367</v>
-      </c>
-      <c r="L3" s="61" t="s">
-        <v>51</v>
-      </c>
-      <c r="M3" s="61" t="s">
-        <v>320</v>
-      </c>
-      <c r="N3" s="61" t="s">
-        <v>322</v>
-      </c>
-      <c r="O3" s="61"/>
-      <c r="P3" s="60"/>
-      <c r="Q3" s="60" t="s">
-        <v>174</v>
-      </c>
-      <c r="R3" s="62" t="s">
-        <v>370</v>
-      </c>
-      <c r="S3" s="63" t="s">
-        <v>333</v>
-      </c>
-      <c r="T3" s="61" t="s">
-        <v>363</v>
-      </c>
-      <c r="U3" s="61" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="s">
-        <v>266</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="21" t="s">
-        <v>325</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="J4" s="18" t="s">
-        <v>241</v>
-      </c>
-      <c r="K4" s="18" t="s">
-        <v>313</v>
-      </c>
-      <c r="L4" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="M4" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="N4" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="O4" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="P4" s="21"/>
-      <c r="Q4" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="R4" s="22" t="s">
-        <v>282</v>
-      </c>
-      <c r="S4" s="29" t="s">
-        <v>334</v>
-      </c>
-      <c r="T4" s="21"/>
-      <c r="U4" s="21"/>
-    </row>
-    <row r="5" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>291</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5" s="16"/>
-      <c r="H5" s="17" t="s">
-        <v>328</v>
-      </c>
-      <c r="I5" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="J5" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="L5" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="M5" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="N5" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="O5" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="P5" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q5" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="R5" s="16" t="s">
-        <v>358</v>
-      </c>
-      <c r="S5" s="43" t="s">
-        <v>335</v>
-      </c>
-      <c r="T5" s="16"/>
-      <c r="U5" s="16"/>
-    </row>
-    <row r="6" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>290</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17" t="s">
-        <v>328</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="K6" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="L6" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="M6" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="N6" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="O6" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="P6" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q6" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="R6" s="16" t="s">
-        <v>358</v>
-      </c>
-      <c r="S6" s="23" t="s">
-        <v>335</v>
-      </c>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16"/>
-    </row>
-    <row r="7" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24" t="s">
-        <v>266</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>288</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="R7" s="27" t="s">
-        <v>359</v>
-      </c>
-      <c r="S7" s="26"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
-    </row>
-    <row r="8" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
-        <v>266</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18" t="s">
-        <v>328</v>
-      </c>
-      <c r="I8" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="J8" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="K8" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="L8" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="M8" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="N8" s="18" t="s">
-        <v>329</v>
-      </c>
-      <c r="O8" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="P8" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q8" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="R8" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="S8" s="29" t="s">
-        <v>334</v>
-      </c>
-      <c r="T8" s="21"/>
-      <c r="U8" s="21"/>
-    </row>
-    <row r="9" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17" t="s">
-        <v>328</v>
-      </c>
-      <c r="I9" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="J9" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="L9" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="M9" s="16"/>
-      <c r="N9" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="O9" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="P9" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q9" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="R9" s="16" t="s">
-        <v>358</v>
-      </c>
-      <c r="S9" s="43"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="16"/>
-    </row>
-    <row r="10" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>292</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="I10" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="J10" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="K10" s="18" t="s">
-        <v>340</v>
-      </c>
-      <c r="L10" s="18"/>
-      <c r="M10" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="N10" s="18" t="s">
-        <v>343</v>
-      </c>
-      <c r="O10" s="21"/>
-      <c r="P10" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q10" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="R10" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="S10" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="T10" s="18"/>
-      <c r="U10" s="18"/>
-    </row>
-    <row r="11" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>292</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="I11" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="J11" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="K11" s="18" t="s">
-        <v>341</v>
-      </c>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="N11" s="18" t="s">
-        <v>342</v>
-      </c>
-      <c r="O11" s="21"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="R11" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="S11" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="T11" s="18"/>
-      <c r="U11" s="18"/>
-    </row>
-    <row r="12" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>292</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="I12" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="K12" s="18" t="s">
-        <v>345</v>
-      </c>
-      <c r="L12" s="18"/>
-      <c r="M12" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="N12" s="18" t="s">
-        <v>344</v>
-      </c>
-      <c r="O12" s="21"/>
-      <c r="P12" s="18"/>
-      <c r="Q12" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="R12" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="S12" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="T12" s="18"/>
-      <c r="U12" s="18"/>
-    </row>
-    <row r="13" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>292</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="I13" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="K13" s="18" t="s">
-        <v>349</v>
-      </c>
-      <c r="L13" s="18"/>
-      <c r="M13" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="N13" s="18" t="s">
-        <v>350</v>
-      </c>
-      <c r="O13" s="21"/>
-      <c r="P13" s="18"/>
-      <c r="Q13" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="R13" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="S13" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="T13" s="18"/>
-      <c r="U13" s="18"/>
-    </row>
-    <row r="14" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>292</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="I14" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="J14" s="18" t="s">
-        <v>348</v>
-      </c>
-      <c r="K14" s="18" t="s">
-        <v>346</v>
-      </c>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="N14" s="18" t="s">
-        <v>347</v>
-      </c>
-      <c r="O14" s="21"/>
-      <c r="P14" s="18"/>
-      <c r="Q14" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="R14" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="S14" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="T14" s="18"/>
-      <c r="U14" s="18"/>
-    </row>
-    <row r="15" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
-        <v>263</v>
-      </c>
-      <c r="B15" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25" t="s">
-        <v>325</v>
-      </c>
-      <c r="I15" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="J15" s="25" t="s">
-        <v>351</v>
-      </c>
-      <c r="K15" s="25" t="s">
-        <v>351</v>
-      </c>
-      <c r="L15" s="25"/>
-      <c r="M15" s="25" t="s">
-        <v>338</v>
-      </c>
-      <c r="N15" s="25" t="s">
-        <v>352</v>
-      </c>
-      <c r="O15" s="24"/>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="R15" s="25" t="s">
-        <v>353</v>
-      </c>
-      <c r="S15" s="26"/>
-      <c r="T15" s="24"/>
-      <c r="U15" s="24"/>
-    </row>
-    <row r="16" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
-        <v>263</v>
-      </c>
-      <c r="B16" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25" t="s">
-        <v>325</v>
-      </c>
-      <c r="I16" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="J16" s="25" t="s">
-        <v>354</v>
-      </c>
-      <c r="K16" s="25" t="s">
-        <v>355</v>
-      </c>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25" t="s">
-        <v>338</v>
-      </c>
-      <c r="N16" s="25" t="s">
-        <v>356</v>
-      </c>
-      <c r="O16" s="24"/>
-      <c r="P16" s="25"/>
-      <c r="Q16" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="R16" s="25" t="s">
-        <v>357</v>
-      </c>
-      <c r="S16" s="26"/>
-      <c r="T16" s="24"/>
-      <c r="U16" s="24"/>
-    </row>
-    <row r="17" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
-        <v>263</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>292</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="I17" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="J17" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="K17" s="18" t="s">
-        <v>336</v>
-      </c>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18" t="s">
-        <v>360</v>
-      </c>
-      <c r="N17" s="18" t="s">
-        <v>361</v>
-      </c>
-      <c r="O17" s="21"/>
-      <c r="P17" s="18" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q17" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="R17" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="S17" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="T17" s="18"/>
-      <c r="U17" s="18"/>
-    </row>
-    <row r="18" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>292</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18" t="s">
-        <v>328</v>
-      </c>
-      <c r="I18" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="J18" s="18" t="s">
-        <v>269</v>
-      </c>
-      <c r="K18" s="18" t="s">
-        <v>337</v>
-      </c>
-      <c r="L18" s="18" t="s">
-        <v>29</v>
       </c>
       <c r="M18" s="18"/>
       <c r="N18" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="O18" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="O18" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="21"/>
+      <c r="R18" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="S18" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="T18" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="U18" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="V18" s="18"/>
+      <c r="W18" s="18"/>
+    </row>
+    <row r="19" spans="1:23" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="18">
+        <v>18</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>385</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="J19" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="L19" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="M19" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="N19" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="O19" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="P18" s="21" t="s">
+      <c r="R19" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="Q18" s="29" t="s">
+      <c r="S19" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="R18" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="S18" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="T18" s="18"/>
-      <c r="U18" s="18"/>
-    </row>
-    <row r="19" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="24" t="s">
+      <c r="T19" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="U19" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="V19" s="18"/>
+      <c r="W19" s="18"/>
+    </row>
+    <row r="20" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="23">
+        <v>19</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="23" t="s">
+        <v>268</v>
+      </c>
+      <c r="K20" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="L20" s="23"/>
+      <c r="M20" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="R20" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="S20" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="T20" s="24"/>
+      <c r="U20" s="23"/>
+      <c r="V20" s="23"/>
+      <c r="W20" s="23"/>
+    </row>
+    <row r="21" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="C21" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="P21" s="18"/>
+      <c r="Q21" s="21"/>
+      <c r="R21" s="21"/>
+      <c r="S21" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="T21" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="U21" s="21"/>
+      <c r="V21" s="21"/>
+      <c r="W21" s="21"/>
+    </row>
+    <row r="22" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="23">
+        <v>21</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="K22" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="R22" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="S22" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="T22" s="24"/>
+      <c r="U22" s="23"/>
+      <c r="V22" s="23"/>
+      <c r="W22" s="23"/>
+    </row>
+    <row r="23" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="16">
+        <v>22</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="D23" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="25" t="s">
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="24" t="s">
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="K23" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="N23" s="16"/>
+      <c r="O23" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="P23" s="16"/>
+      <c r="Q23" s="16"/>
+      <c r="R23" s="16"/>
+      <c r="S23" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="T23" s="16" t="s">
+        <v>348</v>
+      </c>
+      <c r="U23" s="17"/>
+      <c r="V23" s="17"/>
+      <c r="W23" s="17"/>
+    </row>
+    <row r="24" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="18">
+        <v>23</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="18" t="s">
+        <v>276</v>
+      </c>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="P24" s="18"/>
+      <c r="Q24" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="R24" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="S24" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="T24" s="18" t="s">
         <v>270</v>
       </c>
-      <c r="J19" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="K19" s="24"/>
-      <c r="L19" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="M19" s="25"/>
-      <c r="N19" s="25"/>
-      <c r="O19" s="24" t="s">
+      <c r="U24" s="21"/>
+      <c r="V24" s="21"/>
+      <c r="W24" s="21"/>
+    </row>
+    <row r="25" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="18">
+        <v>24</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>266</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="D25" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+      <c r="J25" s="18" t="s">
+        <v>277</v>
+      </c>
+      <c r="K25" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="P19" s="24" t="s">
+      <c r="N25" s="18"/>
+      <c r="O25" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="R25" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="S25" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="T25" s="18" t="s">
+        <v>270</v>
+      </c>
+      <c r="U25" s="21"/>
+      <c r="V25" s="21"/>
+      <c r="W25" s="21"/>
+    </row>
+    <row r="26" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="18">
+        <v>25</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="K26" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="P26" s="18"/>
+      <c r="Q26" s="18"/>
+      <c r="R26" s="18"/>
+      <c r="S26" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="T26" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="U26" s="21"/>
+      <c r="V26" s="21"/>
+      <c r="W26" s="21"/>
+    </row>
+    <row r="27" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="18">
+        <v>26</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="G27" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="K27" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="Q19" s="26" t="s">
+      <c r="N27" s="18"/>
+      <c r="O27" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="R27" s="21"/>
+      <c r="S27" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="T27" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="U27" s="21"/>
+      <c r="V27" s="21"/>
+      <c r="W27" s="21"/>
+    </row>
+    <row r="28" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="17">
+        <v>27</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="S28" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="R19" s="25"/>
-      <c r="S19" s="26"/>
-      <c r="T19" s="24"/>
-      <c r="U19" s="24"/>
-    </row>
-    <row r="20" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="B20" s="35" t="s">
-        <v>294</v>
-      </c>
-      <c r="C20" s="18" t="s">
+      <c r="T28" s="17"/>
+      <c r="U28" s="17"/>
+      <c r="V28" s="17"/>
+      <c r="W28" s="17"/>
+    </row>
+    <row r="29" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="18">
+        <v>28</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="K29" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="O29" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="R29" s="21"/>
+      <c r="S29" s="18"/>
+      <c r="T29" s="18"/>
+      <c r="U29" s="21"/>
+      <c r="V29" s="21"/>
+      <c r="W29" s="21"/>
+    </row>
+    <row r="30" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="24">
+        <v>29</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="D30" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="21" t="s">
-        <v>297</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18" t="s">
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="K30" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="L30" s="24"/>
+      <c r="M30" s="24"/>
+      <c r="N30" s="23"/>
+      <c r="O30" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="P30" s="23"/>
+      <c r="Q30" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="R30" s="23"/>
+      <c r="S30" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="T30" s="24"/>
+      <c r="U30" s="24"/>
+      <c r="V30" s="24"/>
+      <c r="W30" s="24"/>
+    </row>
+    <row r="31" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="11">
+        <v>30</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="L31" s="11"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="11"/>
+      <c r="O31" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="P31" s="11"/>
+      <c r="Q31" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="R31" s="14"/>
+      <c r="S31" s="14"/>
+      <c r="T31" s="11"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="14"/>
+      <c r="W31" s="14"/>
+    </row>
+    <row r="32" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="21">
+        <v>31</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="D32" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="21"/>
+      <c r="K32" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="L32" s="21"/>
+      <c r="M32" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="P32" s="18"/>
+      <c r="Q32" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="M20" s="18"/>
-      <c r="N20" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="O20" s="21"/>
-      <c r="P20" s="21"/>
-      <c r="Q20" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="R20" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="S20" s="29"/>
-      <c r="T20" s="21"/>
-      <c r="U20" s="21"/>
-    </row>
-    <row r="21" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="B21" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="C21" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="J21" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="K21" s="25"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="P21" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q21" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="R21" s="25"/>
-      <c r="S21" s="26"/>
-      <c r="T21" s="24"/>
-      <c r="U21" s="24"/>
-    </row>
-    <row r="22" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="B22" s="43" t="s">
-        <v>294</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="J22" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16" t="s">
+      <c r="R32" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="S32" s="21"/>
+      <c r="T32" s="18"/>
+      <c r="U32" s="21"/>
+      <c r="V32" s="21"/>
+      <c r="W32" s="21"/>
+    </row>
+    <row r="33" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="16">
+        <v>32</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="L33" s="16"/>
+      <c r="M33" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="N33" s="16"/>
+      <c r="O33" s="16"/>
+      <c r="P33" s="16"/>
+      <c r="Q33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="R33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="S33" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
-      <c r="Q22" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="R22" s="16" t="s">
-        <v>358</v>
-      </c>
-      <c r="S22" s="28"/>
-      <c r="T22" s="17"/>
-      <c r="U22" s="17"/>
-    </row>
-    <row r="23" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="B23" s="35" t="s">
-        <v>300</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="18" t="s">
-        <v>278</v>
-      </c>
-      <c r="K23" s="18"/>
-      <c r="L23" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="M23" s="18"/>
-      <c r="N23" s="18" t="s">
-        <v>275</v>
-      </c>
-      <c r="O23" s="18" t="s">
-        <v>281</v>
-      </c>
-      <c r="P23" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="Q23" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="R23" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="S23" s="29"/>
-      <c r="T23" s="21"/>
-      <c r="U23" s="21"/>
-    </row>
-    <row r="24" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="B24" s="21" t="s">
-        <v>300</v>
-      </c>
-      <c r="C24" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="F24" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18" t="s">
-        <v>279</v>
-      </c>
-      <c r="J24" s="18" t="s">
-        <v>268</v>
-      </c>
-      <c r="K24" s="18"/>
-      <c r="L24" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="M24" s="18"/>
-      <c r="N24" s="18" t="s">
-        <v>275</v>
-      </c>
-      <c r="O24" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="P24" s="18" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q24" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="R24" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="S24" s="29"/>
-      <c r="T24" s="21"/>
-      <c r="U24" s="21"/>
-    </row>
-    <row r="25" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="B25" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="18"/>
-      <c r="E25" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="F25" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="J25" s="18" t="s">
-        <v>265</v>
-      </c>
-      <c r="K25" s="18"/>
-      <c r="L25" s="18"/>
-      <c r="M25" s="18"/>
-      <c r="N25" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="O25" s="18"/>
-      <c r="P25" s="18"/>
-      <c r="Q25" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="R25" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="S25" s="29"/>
-      <c r="T25" s="21"/>
-      <c r="U25" s="21"/>
-    </row>
-    <row r="26" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="B26" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="C26" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="D26" s="18"/>
-      <c r="E26" s="31" t="s">
-        <v>307</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>160</v>
-      </c>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="J26" s="18" t="s">
-        <v>237</v>
-      </c>
-      <c r="K26" s="18"/>
-      <c r="L26" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="M26" s="18"/>
-      <c r="N26" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="O26" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="R26" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="S26" s="29"/>
-      <c r="T26" s="21"/>
-      <c r="U26" s="21"/>
-    </row>
-    <row r="27" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="17" t="s">
-        <v>298</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="J27" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="K27" s="17"/>
-      <c r="L27" s="17"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="16" t="s">
-        <v>173</v>
-      </c>
-      <c r="O27" s="16"/>
-      <c r="P27" s="17" t="s">
-        <v>304</v>
-      </c>
-      <c r="Q27" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="R27" s="17"/>
-      <c r="S27" s="28"/>
-      <c r="T27" s="17"/>
-      <c r="U27" s="17"/>
-    </row>
-    <row r="28" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="B28" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18" t="s">
-        <v>162</v>
-      </c>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="J28" s="18" t="s">
-        <v>165</v>
-      </c>
-      <c r="K28" s="18"/>
-      <c r="L28" s="18"/>
-      <c r="M28" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="N28" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="O28" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="P28" s="21"/>
-      <c r="Q28" s="22"/>
-      <c r="R28" s="18"/>
-      <c r="S28" s="29"/>
-      <c r="T28" s="21"/>
-      <c r="U28" s="21"/>
-    </row>
-    <row r="29" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="B29" s="42" t="s">
-        <v>303</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="24" t="s">
-        <v>168</v>
-      </c>
-      <c r="J29" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="K29" s="25"/>
-      <c r="L29" s="25"/>
-      <c r="M29" s="24"/>
-      <c r="N29" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="O29" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="P29" s="24"/>
-      <c r="Q29" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="R29" s="25"/>
-      <c r="S29" s="27"/>
-      <c r="T29" s="25"/>
-      <c r="U29" s="25"/>
-    </row>
-    <row r="30" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="33" t="s">
-        <v>267</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>267</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="F30" s="11" t="s">
-        <v>212</v>
-      </c>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="J30" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="O30" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="P30" s="14"/>
-      <c r="Q30" s="34"/>
-      <c r="R30" s="11"/>
-      <c r="S30" s="34"/>
-      <c r="T30" s="14"/>
-      <c r="U30" s="14"/>
-    </row>
-    <row r="31" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="35" t="s">
-        <v>284</v>
-      </c>
-      <c r="B31" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="C31" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18" t="s">
-        <v>186</v>
-      </c>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="K31" s="21"/>
-      <c r="L31" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="M31" s="18"/>
-      <c r="N31" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="O31" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="P31" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q31" s="29"/>
-      <c r="R31" s="18"/>
-      <c r="S31" s="29"/>
-      <c r="T31" s="21"/>
-      <c r="U31" s="21"/>
-    </row>
-    <row r="32" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>286</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="J32" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="M32" s="16"/>
-      <c r="N32" s="16"/>
-      <c r="O32" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="P32" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q32" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="R32" s="17"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="17"/>
-      <c r="U32" s="17"/>
-    </row>
-    <row r="33" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>286</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17" t="s">
-        <v>243</v>
-      </c>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="M33" s="16"/>
-      <c r="N33" s="16" t="s">
-        <v>174</v>
-      </c>
-      <c r="O33" s="16" t="s">
-        <v>283</v>
-      </c>
-      <c r="P33" s="16"/>
-      <c r="Q33" s="23"/>
-      <c r="R33" s="17" t="s">
-        <v>234</v>
-      </c>
-      <c r="S33" s="28"/>
       <c r="T33" s="17"/>
       <c r="U33" s="17"/>
-    </row>
-    <row r="34" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
-        <v>264</v>
+      <c r="V33" s="17"/>
+      <c r="W33" s="17"/>
+    </row>
+    <row r="34" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="16">
+        <v>33</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>287</v>
-      </c>
-      <c r="C34" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="D34" s="17"/>
+        <v>282</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>284</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>48</v>
+      </c>
       <c r="E34" s="17"/>
-      <c r="F34" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="J34" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="M34" s="16"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17" t="s">
+        <v>243</v>
+      </c>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="16"/>
+      <c r="K34" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="L34" s="17"/>
+      <c r="M34" s="17" t="s">
+        <v>33</v>
+      </c>
       <c r="N34" s="16"/>
       <c r="O34" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="P34" s="16"/>
+      <c r="Q34" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="R34" s="16"/>
+      <c r="S34" s="16"/>
+      <c r="T34" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="U34" s="17"/>
+      <c r="V34" s="17"/>
+      <c r="W34" s="17"/>
+    </row>
+    <row r="35" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="16">
+        <v>34</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="D35" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="16"/>
+      <c r="M35" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="N35" s="16"/>
+      <c r="O35" s="16"/>
+      <c r="P35" s="16"/>
+      <c r="Q35" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="P34" s="16" t="s">
+      <c r="R35" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="Q34" s="23" t="s">
+      <c r="S35" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="R34" s="16"/>
-      <c r="S34" s="28"/>
-      <c r="T34" s="17"/>
-      <c r="U34" s="17"/>
-    </row>
-    <row r="35" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="B35" s="21" t="s">
-        <v>264</v>
-      </c>
-      <c r="C35" s="18" t="s">
+      <c r="T35" s="16"/>
+      <c r="U35" s="17"/>
+      <c r="V35" s="17"/>
+      <c r="W35" s="17"/>
+    </row>
+    <row r="36" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="21">
+        <v>35</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="D36" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18" t="s">
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="G35" s="18"/>
-      <c r="H35" s="18"/>
-      <c r="I35" s="21" t="s">
+      <c r="H36" s="18"/>
+      <c r="I36" s="18"/>
+      <c r="J36" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="J35" s="18" t="s">
+      <c r="K36" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="K35" s="18"/>
-      <c r="L35" s="18"/>
-      <c r="M35" s="21"/>
-      <c r="N35" s="21"/>
-      <c r="O35" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="P35" s="21"/>
-      <c r="Q35" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="R35" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="S35" s="29"/>
-      <c r="T35" s="21"/>
-      <c r="U35" s="21"/>
-    </row>
-    <row r="36" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="21"/>
-      <c r="B36" s="21"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="G36" s="21"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="21"/>
-      <c r="J36" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="K36" s="21"/>
-      <c r="L36" s="18" t="s">
-        <v>42</v>
-      </c>
+      <c r="L36" s="18"/>
       <c r="M36" s="18"/>
-      <c r="N36" s="18" t="s">
-        <v>93</v>
-      </c>
+      <c r="N36" s="21"/>
       <c r="O36" s="21"/>
       <c r="P36" s="21"/>
-      <c r="Q36" s="29"/>
+      <c r="Q36" s="21" t="s">
+        <v>217</v>
+      </c>
       <c r="R36" s="21"/>
-      <c r="S36" s="29"/>
-      <c r="T36" s="21"/>
+      <c r="S36" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="T36" s="18" t="s">
+        <v>218</v>
+      </c>
       <c r="U36" s="21"/>
-    </row>
-    <row r="37" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="24"/>
-      <c r="B37" s="24"/>
-      <c r="C37" s="25" t="s">
+      <c r="V36" s="21"/>
+      <c r="W36" s="21"/>
+    </row>
+    <row r="37" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="21">
+        <v>36</v>
+      </c>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="H37" s="21"/>
+      <c r="I37" s="21"/>
+      <c r="J37" s="21"/>
+      <c r="K37" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="L37" s="21"/>
+      <c r="M37" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="P37" s="18"/>
+      <c r="Q37" s="21"/>
+      <c r="R37" s="21"/>
+      <c r="S37" s="28"/>
+      <c r="T37" s="21"/>
+      <c r="U37" s="28"/>
+      <c r="V37" s="21"/>
+      <c r="W37" s="21"/>
+    </row>
+    <row r="38" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="23">
+        <v>37</v>
+      </c>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25" t="s">
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="G37" s="25"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="24" t="s">
+      <c r="H38" s="24"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="J37" s="25" t="s">
+      <c r="K38" s="24" t="s">
         <v>214</v>
       </c>
-      <c r="K37" s="25"/>
-      <c r="L37" s="25" t="s">
+      <c r="L38" s="24"/>
+      <c r="M38" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="M37" s="24"/>
-      <c r="N37" s="24" t="s">
-        <v>274</v>
-      </c>
-      <c r="O37" s="24" t="s">
+      <c r="N38" s="23"/>
+      <c r="O38" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="P38" s="23"/>
+      <c r="Q38" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="R38" s="24" t="s">
         <v>261</v>
       </c>
-      <c r="P37" s="25" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q37" s="26" t="s">
+      <c r="S38" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="R37" s="25" t="s">
+      <c r="T38" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="S37" s="27"/>
-      <c r="T37" s="25"/>
-      <c r="U37" s="25"/>
-    </row>
-    <row r="38" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="B38" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="C38" s="18" t="s">
+      <c r="U38" s="26"/>
+      <c r="V38" s="24"/>
+      <c r="W38" s="24"/>
+    </row>
+    <row r="39" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="21">
+        <v>38</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="D39" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18" t="s">
+      <c r="E39" s="18"/>
+      <c r="F39" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="F38" s="18" t="s">
+      <c r="G39" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="18" t="s">
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="J38" s="18" t="s">
+      <c r="K39" s="18" t="s">
+        <v>257</v>
+      </c>
+      <c r="L39" s="18"/>
+      <c r="M39" s="18"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="18" t="s">
         <v>258</v>
       </c>
-      <c r="K38" s="18"/>
-      <c r="L38" s="18"/>
-      <c r="M38" s="18"/>
-      <c r="N38" s="18" t="s">
+      <c r="P39" s="18"/>
+      <c r="Q39" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="R39" s="18" t="s">
+        <v>306</v>
+      </c>
+      <c r="S39" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="T39" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="U39" s="28"/>
+      <c r="V39" s="21"/>
+      <c r="W39" s="21"/>
+    </row>
+    <row r="40" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="14">
+        <v>39</v>
+      </c>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="O38" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="P38" s="18" t="s">
-        <v>309</v>
-      </c>
-      <c r="Q38" s="22" t="s">
+      <c r="P40" s="11"/>
+      <c r="Q40" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="R40" s="14"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="R38" s="18" t="s">
-        <v>89</v>
-      </c>
-      <c r="S38" s="29"/>
-      <c r="T38" s="21"/>
-      <c r="U38" s="21"/>
-    </row>
-    <row r="39" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="14"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11"/>
-      <c r="I39" s="14" t="s">
+      <c r="U40" s="30"/>
+      <c r="V40" s="14"/>
+      <c r="W40" s="14"/>
+    </row>
+    <row r="41" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="14">
+        <v>40</v>
+      </c>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="14"/>
+      <c r="O41" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="P41" s="14"/>
+      <c r="Q41" s="14"/>
+      <c r="R41" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="S41" s="30"/>
+      <c r="T41" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="U41" s="30"/>
+      <c r="V41" s="14"/>
+      <c r="W41" s="14"/>
+    </row>
+    <row r="42" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="14">
+        <v>41</v>
+      </c>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E42" s="11"/>
+      <c r="F42" s="11"/>
+      <c r="G42" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="J39" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="O39" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="P39" s="14"/>
-      <c r="Q39" s="34"/>
-      <c r="R39" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="S39" s="34"/>
-      <c r="T39" s="14"/>
-      <c r="U39" s="14"/>
-    </row>
-    <row r="40" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="14"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="14"/>
-      <c r="N40" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="O40" s="14"/>
-      <c r="P40" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q40" s="34"/>
-      <c r="R40" s="11" t="s">
-        <v>207</v>
-      </c>
-      <c r="S40" s="34"/>
-      <c r="T40" s="14"/>
-      <c r="U40" s="14"/>
-    </row>
-    <row r="41" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="14"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11" t="s">
-        <v>162</v>
-      </c>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="J41" s="11" t="s">
+      <c r="K42" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="O41" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="P41" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q41" s="34"/>
-      <c r="R41" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="S41" s="34"/>
-      <c r="T41" s="14"/>
-      <c r="U41" s="14"/>
-    </row>
-    <row r="42" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="14"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11" t="s">
-        <v>199</v>
-      </c>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="J42" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="K42" s="11"/>
       <c r="L42" s="11"/>
       <c r="M42" s="11"/>
-      <c r="N42" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="O42" s="14"/>
-      <c r="P42" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q42" s="34"/>
-      <c r="R42" s="11"/>
-      <c r="S42" s="34"/>
-      <c r="T42" s="14"/>
-      <c r="U42" s="14"/>
-    </row>
-    <row r="43" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="14"/>
+      <c r="N42" s="14"/>
+      <c r="O42" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="P42" s="14"/>
+      <c r="Q42" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="R42" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="S42" s="30"/>
+      <c r="T42" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="U42" s="30"/>
+      <c r="V42" s="14"/>
+      <c r="W42" s="14"/>
+    </row>
+    <row r="43" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="14">
+        <v>42</v>
+      </c>
       <c r="B43" s="14"/>
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="14"/>
+      <c r="D43" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D43" s="11"/>
       <c r="E43" s="11"/>
-      <c r="F43" s="11" t="s">
+      <c r="F43" s="11"/>
+      <c r="G43" s="11" t="s">
         <v>199</v>
       </c>
-      <c r="G43" s="11"/>
       <c r="H43" s="11"/>
-      <c r="I43" s="14"/>
-      <c r="J43" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="K43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>200</v>
+      </c>
       <c r="L43" s="11"/>
       <c r="M43" s="11"/>
-      <c r="N43" s="11" t="s">
+      <c r="N43" s="11"/>
+      <c r="O43" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="P43" s="11"/>
+      <c r="Q43" s="14"/>
+      <c r="R43" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="S43" s="30"/>
+      <c r="T43" s="11"/>
+      <c r="U43" s="30"/>
+      <c r="V43" s="14"/>
+      <c r="W43" s="14"/>
+    </row>
+    <row r="44" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="14">
+        <v>43</v>
+      </c>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="O43" s="14" t="s">
+      <c r="P44" s="11"/>
+      <c r="Q44" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="P43" s="14"/>
-      <c r="Q43" s="34"/>
-      <c r="R43" s="11"/>
-      <c r="S43" s="34"/>
-      <c r="T43" s="14"/>
-      <c r="U43" s="14"/>
-    </row>
-    <row r="44" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="14"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="11" t="s">
+      <c r="R44" s="14"/>
+      <c r="S44" s="30"/>
+      <c r="T44" s="11"/>
+      <c r="U44" s="30"/>
+      <c r="V44" s="14"/>
+      <c r="W44" s="14"/>
+    </row>
+    <row r="45" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="14">
+        <v>44</v>
+      </c>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11" t="s">
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="14"/>
-      <c r="J44" s="11" t="s">
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="14"/>
+      <c r="K45" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="14"/>
-      <c r="N44" s="14"/>
-      <c r="O44" s="14" t="s">
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+      <c r="N45" s="14"/>
+      <c r="O45" s="14"/>
+      <c r="P45" s="14"/>
+      <c r="Q45" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="P44" s="11" t="s">
+      <c r="R45" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="Q44" s="14"/>
-      <c r="R44" s="11"/>
-      <c r="S44" s="34"/>
-      <c r="T44" s="14"/>
-      <c r="U44" s="14"/>
-    </row>
-    <row r="45" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="8"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="9" t="s">
+      <c r="S45" s="14"/>
+      <c r="T45" s="11"/>
+      <c r="U45" s="30"/>
+      <c r="V45" s="14"/>
+      <c r="W45" s="14"/>
+    </row>
+    <row r="46" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="8">
+        <v>45</v>
+      </c>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9" t="s">
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="G45" s="9"/>
-      <c r="H45" s="9"/>
-      <c r="I45" s="8"/>
-      <c r="J45" s="9" t="s">
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
-      <c r="M45" s="8"/>
-      <c r="N45" s="8" t="s">
+      <c r="L46" s="9"/>
+      <c r="M46" s="9"/>
+      <c r="N46" s="8"/>
+      <c r="O46" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="O45" s="8" t="s">
+      <c r="P46" s="8"/>
+      <c r="Q46" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="P45" s="8"/>
-      <c r="Q45" s="36"/>
-      <c r="R45" s="11"/>
-      <c r="S45" s="34"/>
-      <c r="T45" s="14"/>
-      <c r="U45" s="14"/>
-    </row>
-    <row r="46" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="9" t="s">
+      <c r="R46" s="8"/>
+      <c r="S46" s="31"/>
+      <c r="T46" s="11"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="14"/>
+      <c r="W46" s="14"/>
+    </row>
+    <row r="47" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="8">
+        <v>46</v>
+      </c>
+      <c r="B47" s="8"/>
+      <c r="C47" s="8"/>
+      <c r="D47" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9" t="s">
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
-      <c r="I46" s="8"/>
-      <c r="J46" s="9" t="s">
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="K46" s="9"/>
-      <c r="L46" s="9"/>
-      <c r="M46" s="8"/>
-      <c r="N46" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="O46" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="P46" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q46" s="36"/>
-      <c r="R46" s="11"/>
-      <c r="S46" s="34"/>
-      <c r="T46" s="14"/>
-      <c r="U46" s="14"/>
-    </row>
-    <row r="47" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="8"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="G47" s="9"/>
-      <c r="H47" s="9"/>
-      <c r="I47" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="J47" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="K47" s="9"/>
       <c r="L47" s="9"/>
       <c r="M47" s="9"/>
-      <c r="N47" s="9" t="s">
+      <c r="N47" s="8"/>
+      <c r="O47" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="P47" s="8"/>
+      <c r="Q47" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="R47" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="S47" s="31"/>
+      <c r="T47" s="11"/>
+      <c r="U47" s="30"/>
+      <c r="V47" s="14"/>
+      <c r="W47" s="14"/>
+    </row>
+    <row r="48" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="8">
+        <v>47</v>
+      </c>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="K48" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="L48" s="9"/>
+      <c r="M48" s="9"/>
+      <c r="N48" s="9"/>
+      <c r="O48" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="O47" s="9" t="s">
+      <c r="P48" s="9"/>
+      <c r="Q48" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="P47" s="8"/>
-      <c r="Q47" s="37"/>
-      <c r="R47" s="11" t="s">
+      <c r="R48" s="8"/>
+      <c r="S48" s="32"/>
+      <c r="T48" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="S47" s="34"/>
-      <c r="T47" s="14"/>
-      <c r="U47" s="14"/>
-    </row>
-    <row r="48" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="9" t="s">
+      <c r="U48" s="30"/>
+      <c r="V48" s="14"/>
+      <c r="W48" s="14"/>
+    </row>
+    <row r="49" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="8">
         <v>48</v>
       </c>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9" t="s">
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="8"/>
-      <c r="J48" s="9" t="s">
+      <c r="H49" s="9"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="K48" s="9"/>
-      <c r="L48" s="9"/>
-      <c r="M48" s="8"/>
-      <c r="N48" s="8" t="s">
+      <c r="L49" s="9"/>
+      <c r="M49" s="9"/>
+      <c r="N49" s="8"/>
+      <c r="O49" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="O48" s="8" t="s">
+      <c r="P49" s="8"/>
+      <c r="Q49" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="P48" s="8"/>
-      <c r="Q48" s="36"/>
-      <c r="R48" s="11" t="s">
+      <c r="R49" s="8"/>
+      <c r="S49" s="31"/>
+      <c r="T49" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="S48" s="34"/>
-      <c r="T48" s="14"/>
-      <c r="U48" s="14"/>
-    </row>
-    <row r="49" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="8"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="9" t="s">
+      <c r="U49" s="30"/>
+      <c r="V49" s="14"/>
+      <c r="W49" s="14"/>
+    </row>
+    <row r="50" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="8">
+        <v>49</v>
+      </c>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9" t="s">
+      <c r="E50" s="9"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="G49" s="9"/>
-      <c r="H49" s="9"/>
-      <c r="I49" s="8"/>
-      <c r="J49" s="9" t="s">
+      <c r="H50" s="9"/>
+      <c r="I50" s="9"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="K49" s="9"/>
-      <c r="L49" s="9"/>
-      <c r="M49" s="8"/>
-      <c r="N49" s="8" t="s">
+      <c r="L50" s="9"/>
+      <c r="M50" s="9"/>
+      <c r="N50" s="8"/>
+      <c r="O50" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="O49" s="8" t="s">
+      <c r="P50" s="8"/>
+      <c r="Q50" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="P49" s="8"/>
-      <c r="Q49" s="36"/>
-      <c r="R49" s="11" t="s">
+      <c r="R50" s="8"/>
+      <c r="S50" s="31"/>
+      <c r="T50" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="S49" s="34"/>
-      <c r="T49" s="14"/>
-      <c r="U49" s="14"/>
-    </row>
-    <row r="50" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="8"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="9" t="s">
+      <c r="U50" s="30"/>
+      <c r="V50" s="14"/>
+      <c r="W50" s="14"/>
+    </row>
+    <row r="51" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="8">
+        <v>50</v>
+      </c>
+      <c r="B51" s="8"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9" t="s">
+      <c r="E51" s="9"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="8"/>
-      <c r="J50" s="9" t="s">
+      <c r="H51" s="9"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="K50" s="9"/>
-      <c r="L50" s="9"/>
-      <c r="M50" s="8"/>
-      <c r="N50" s="8" t="s">
+      <c r="L51" s="9"/>
+      <c r="M51" s="9"/>
+      <c r="N51" s="8"/>
+      <c r="O51" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="O50" s="8" t="s">
+      <c r="P51" s="8"/>
+      <c r="Q51" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="P50" s="8"/>
-      <c r="Q50" s="36"/>
-      <c r="R50" s="11" t="s">
+      <c r="R51" s="8"/>
+      <c r="S51" s="31"/>
+      <c r="T51" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="S50" s="34"/>
-      <c r="T50" s="14"/>
-      <c r="U50" s="14"/>
-    </row>
-    <row r="51" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="8"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="9" t="s">
+      <c r="U51" s="30"/>
+      <c r="V51" s="14"/>
+      <c r="W51" s="14"/>
+    </row>
+    <row r="52" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="8">
+        <v>51</v>
+      </c>
+      <c r="B52" s="8"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9" t="s">
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="G51" s="9"/>
-      <c r="H51" s="9"/>
-      <c r="I51" s="8"/>
-      <c r="J51" s="9" t="s">
+      <c r="H52" s="9"/>
+      <c r="I52" s="9"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="K51" s="9"/>
-      <c r="L51" s="9"/>
-      <c r="M51" s="8"/>
-      <c r="N51" s="8" t="s">
+      <c r="L52" s="9"/>
+      <c r="M52" s="9"/>
+      <c r="N52" s="8"/>
+      <c r="O52" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="O51" s="8" t="s">
+      <c r="P52" s="8"/>
+      <c r="Q52" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="P51" s="8"/>
-      <c r="Q51" s="36"/>
-      <c r="R51" s="11" t="s">
+      <c r="R52" s="8"/>
+      <c r="S52" s="31"/>
+      <c r="T52" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="S51" s="34"/>
-      <c r="T51" s="14"/>
-      <c r="U51" s="14"/>
-    </row>
-    <row r="52" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="38"/>
-      <c r="B52" s="38"/>
-      <c r="C52" s="39" t="s">
+      <c r="U52" s="30"/>
+      <c r="V52" s="14"/>
+      <c r="W52" s="14"/>
+    </row>
+    <row r="53" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="33">
+        <v>52</v>
+      </c>
+      <c r="B53" s="33"/>
+      <c r="C53" s="33"/>
+      <c r="D53" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="D52" s="39"/>
-      <c r="E52" s="39"/>
-      <c r="F52" s="39" t="s">
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="34" t="s">
         <v>212</v>
       </c>
-      <c r="G52" s="39"/>
-      <c r="H52" s="39"/>
-      <c r="I52" s="38"/>
-      <c r="J52" s="39" t="s">
+      <c r="H53" s="34"/>
+      <c r="I53" s="34"/>
+      <c r="J53" s="33"/>
+      <c r="K53" s="34" t="s">
         <v>235</v>
       </c>
-      <c r="K52" s="39"/>
-      <c r="L52" s="39" t="s">
+      <c r="L53" s="34"/>
+      <c r="M53" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="M52" s="38"/>
-      <c r="N52" s="38" t="s">
+      <c r="N53" s="33"/>
+      <c r="O53" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="O52" s="39" t="s">
+      <c r="P53" s="33"/>
+      <c r="Q53" s="34" t="s">
         <v>236</v>
       </c>
-      <c r="P52" s="38"/>
-      <c r="Q52" s="40"/>
-      <c r="R52" s="17" t="s">
+      <c r="R53" s="33"/>
+      <c r="S53" s="35"/>
+      <c r="T53" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="S52" s="28"/>
-      <c r="T52" s="17"/>
-      <c r="U52" s="17"/>
-    </row>
-    <row r="53" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="8"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="9" t="s">
+      <c r="U53" s="27"/>
+      <c r="V53" s="17"/>
+      <c r="W53" s="17"/>
+    </row>
+    <row r="54" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="8">
+        <v>53</v>
+      </c>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9" t="s">
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
-      <c r="I53" s="8" t="s">
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="J53" s="9" t="s">
+      <c r="K54" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="K53" s="9"/>
-      <c r="L53" s="9"/>
-      <c r="M53" s="9"/>
-      <c r="N53" s="9" t="s">
+      <c r="L54" s="9"/>
+      <c r="M54" s="9"/>
+      <c r="N54" s="9"/>
+      <c r="O54" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="O53" s="8" t="s">
+      <c r="P54" s="9"/>
+      <c r="Q54" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="P53" s="8" t="s">
+      <c r="R54" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="Q53" s="36"/>
-      <c r="R53" s="11" t="s">
+      <c r="S54" s="31"/>
+      <c r="T54" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="S53" s="34"/>
-      <c r="T53" s="14"/>
-      <c r="U53" s="14"/>
-    </row>
-    <row r="54" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="8"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="9" t="s">
+      <c r="U54" s="30"/>
+      <c r="V54" s="14"/>
+      <c r="W54" s="14"/>
+    </row>
+    <row r="55" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="8">
+        <v>54</v>
+      </c>
+      <c r="B55" s="8"/>
+      <c r="C55" s="8"/>
+      <c r="D55" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9" t="s">
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
-      <c r="I54" s="8" t="s">
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="J54" s="9" t="s">
+      <c r="K55" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="K54" s="9"/>
-      <c r="L54" s="9"/>
-      <c r="M54" s="8"/>
-      <c r="N54" s="8" t="s">
+      <c r="L55" s="9"/>
+      <c r="M55" s="9"/>
+      <c r="N55" s="8"/>
+      <c r="O55" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="O54" s="9" t="s">
+      <c r="P55" s="8"/>
+      <c r="Q55" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="P54" s="8"/>
-      <c r="Q54" s="36"/>
-      <c r="R54" s="45" t="s">
+      <c r="R55" s="8"/>
+      <c r="S55" s="31"/>
+      <c r="T55" s="37" t="s">
         <v>234</v>
       </c>
-      <c r="T54" s="14"/>
-      <c r="U54" s="14"/>
-    </row>
-    <row r="55" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="8"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="9" t="s">
+      <c r="V55" s="14"/>
+      <c r="W55" s="14"/>
+    </row>
+    <row r="56" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="33">
+        <v>55</v>
+      </c>
+      <c r="B56" s="33"/>
+      <c r="C56" s="33"/>
+      <c r="D56" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9" t="s">
+      <c r="E56" s="34"/>
+      <c r="F56" s="34"/>
+      <c r="G56" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="8" t="s">
+      <c r="H56" s="34"/>
+      <c r="I56" s="34"/>
+      <c r="J56" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="J55" s="9" t="s">
+      <c r="K56" s="34" t="s">
         <v>245</v>
       </c>
-      <c r="K55" s="9"/>
-      <c r="L55" s="9"/>
-      <c r="M55" s="8"/>
-      <c r="N55" s="8" t="s">
+      <c r="L56" s="34"/>
+      <c r="M56" s="34"/>
+      <c r="N56" s="33"/>
+      <c r="O56" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="O55" s="9" t="s">
+      <c r="P56" s="33"/>
+      <c r="Q56" s="34" t="s">
         <v>247</v>
       </c>
-      <c r="P55" s="8"/>
-      <c r="Q55" s="36"/>
-      <c r="R55" s="37" t="s">
+      <c r="R56" s="33"/>
+      <c r="S56" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="T56" s="53" t="s">
         <v>234</v>
       </c>
-      <c r="T55" s="14"/>
-      <c r="U55" s="14"/>
-    </row>
-    <row r="56" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="8"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="9" t="s">
+      <c r="U56" s="54"/>
+      <c r="V56" s="16"/>
+      <c r="W56" s="16"/>
+    </row>
+    <row r="57" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="33">
+        <v>56</v>
+      </c>
+      <c r="B57" s="33"/>
+      <c r="C57" s="33"/>
+      <c r="D57" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9" t="s">
+      <c r="E57" s="34"/>
+      <c r="F57" s="34"/>
+      <c r="G57" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="G56" s="9"/>
-      <c r="H56" s="9"/>
-      <c r="I56" s="8" t="s">
+      <c r="H57" s="34"/>
+      <c r="I57" s="34"/>
+      <c r="J57" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="J56" s="9" t="s">
+      <c r="K57" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="K56" s="9"/>
-      <c r="L56" s="9"/>
-      <c r="M56" s="8"/>
-      <c r="N56" s="8" t="s">
+      <c r="L57" s="34"/>
+      <c r="M57" s="34"/>
+      <c r="N57" s="33"/>
+      <c r="O57" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="O56" s="9" t="s">
+      <c r="P57" s="33"/>
+      <c r="Q57" s="34" t="s">
         <v>247</v>
       </c>
-      <c r="P56" s="8"/>
-      <c r="Q56" s="36"/>
-      <c r="R56" s="37" t="s">
+      <c r="R57" s="33"/>
+      <c r="S57" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="T57" s="53" t="s">
         <v>234</v>
       </c>
-      <c r="T56" s="14"/>
-      <c r="U56" s="14"/>
-    </row>
-    <row r="57" spans="1:21" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="8"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="9" t="s">
+      <c r="U57" s="54"/>
+      <c r="V57" s="16"/>
+      <c r="W57" s="16"/>
+    </row>
+    <row r="58" spans="1:23" ht="50.1" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="33">
+        <v>57</v>
+      </c>
+      <c r="B58" s="33"/>
+      <c r="C58" s="33"/>
+      <c r="D58" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9" t="s">
+      <c r="E58" s="34"/>
+      <c r="F58" s="34"/>
+      <c r="G58" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="G57" s="9"/>
-      <c r="H57" s="9"/>
-      <c r="I57" s="8" t="s">
+      <c r="H58" s="34"/>
+      <c r="I58" s="34"/>
+      <c r="J58" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="J57" s="9" t="s">
+      <c r="K58" s="34" t="s">
         <v>248</v>
       </c>
-      <c r="K57" s="9"/>
-      <c r="L57" s="9"/>
-      <c r="M57" s="8"/>
-      <c r="N57" s="8" t="s">
+      <c r="L58" s="34"/>
+      <c r="M58" s="34"/>
+      <c r="N58" s="33"/>
+      <c r="O58" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="O57" s="9" t="s">
+      <c r="P58" s="33"/>
+      <c r="Q58" s="34" t="s">
         <v>250</v>
       </c>
-      <c r="P57" s="8"/>
-      <c r="Q57" s="36"/>
-      <c r="R57" s="37" t="s">
+      <c r="R58" s="33"/>
+      <c r="S58" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="T58" s="53" t="s">
         <v>234</v>
       </c>
-      <c r="T57" s="14"/>
-      <c r="U57" s="14"/>
+      <c r="U58" s="54"/>
+      <c r="V58" s="16"/>
+      <c r="W58" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5200,10 +5641,10 @@
       </c>
     </row>
     <row r="3" spans="1:16" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="56"/>
+      <c r="B3" s="49"/>
       <c r="C3" s="3" t="s">
         <v>5</v>
       </c>
@@ -5234,8 +5675,8 @@
       <c r="P3" s="3"/>
     </row>
     <row r="4" spans="1:16" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="51"/>
-      <c r="B4" s="57"/>
+      <c r="A4" s="44"/>
+      <c r="B4" s="50"/>
       <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
@@ -5268,8 +5709,8 @@
       <c r="P4" s="3"/>
     </row>
     <row r="5" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="52"/>
-      <c r="B5" s="58"/>
+      <c r="A5" s="45"/>
+      <c r="B5" s="51"/>
       <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
@@ -5302,10 +5743,10 @@
       <c r="P5" s="3"/>
     </row>
     <row r="6" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="53" t="s">
+      <c r="A6" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="40" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -5320,7 +5761,7 @@
       <c r="F6" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="G6" s="47" t="s">
+      <c r="G6" s="40" t="s">
         <v>91</v>
       </c>
       <c r="H6" s="4" t="s">
@@ -5340,8 +5781,8 @@
       <c r="P6" s="3"/>
     </row>
     <row r="7" spans="1:16" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="54"/>
-      <c r="B7" s="48"/>
+      <c r="A7" s="47"/>
+      <c r="B7" s="41"/>
       <c r="C7" s="3" t="s">
         <v>10</v>
       </c>
@@ -5354,7 +5795,7 @@
       <c r="F7" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G7" s="48"/>
+      <c r="G7" s="41"/>
       <c r="H7" s="4" t="s">
         <v>48</v>
       </c>
@@ -5372,8 +5813,8 @@
       <c r="P7" s="3"/>
     </row>
     <row r="8" spans="1:16" ht="150" x14ac:dyDescent="0.25">
-      <c r="A8" s="54"/>
-      <c r="B8" s="48"/>
+      <c r="A8" s="47"/>
+      <c r="B8" s="41"/>
       <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
@@ -5386,7 +5827,7 @@
       <c r="F8" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="G8" s="48"/>
+      <c r="G8" s="41"/>
       <c r="H8" s="4" t="s">
         <v>50</v>
       </c>
@@ -5404,8 +5845,8 @@
       <c r="P8" s="3"/>
     </row>
     <row r="9" spans="1:16" ht="75" x14ac:dyDescent="0.25">
-      <c r="A9" s="54"/>
-      <c r="B9" s="48"/>
+      <c r="A9" s="47"/>
+      <c r="B9" s="41"/>
       <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
@@ -5416,7 +5857,7 @@
         <v>55</v>
       </c>
       <c r="F9" s="4"/>
-      <c r="G9" s="48"/>
+      <c r="G9" s="41"/>
       <c r="H9" s="4" t="s">
         <v>50</v>
       </c>
@@ -5434,8 +5875,8 @@
       <c r="P9" s="3"/>
     </row>
     <row r="10" spans="1:16" ht="75" x14ac:dyDescent="0.25">
-      <c r="A10" s="54"/>
-      <c r="B10" s="48"/>
+      <c r="A10" s="47"/>
+      <c r="B10" s="41"/>
       <c r="C10" s="3" t="s">
         <v>12</v>
       </c>
@@ -5448,7 +5889,7 @@
       <c r="F10" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G10" s="48"/>
+      <c r="G10" s="41"/>
       <c r="H10" s="4" t="s">
         <v>50</v>
       </c>
@@ -5466,8 +5907,8 @@
       <c r="P10" s="3"/>
     </row>
     <row r="11" spans="1:16" ht="60" x14ac:dyDescent="0.25">
-      <c r="A11" s="55"/>
-      <c r="B11" s="49"/>
+      <c r="A11" s="48"/>
+      <c r="B11" s="42"/>
       <c r="C11" s="3" t="s">
         <v>13</v>
       </c>
@@ -5480,7 +5921,7 @@
       <c r="F11" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="G11" s="49"/>
+      <c r="G11" s="42"/>
       <c r="H11" s="4" t="s">
         <v>48</v>
       </c>
@@ -5498,10 +5939,10 @@
       <c r="P11" s="3"/>
     </row>
     <row r="12" spans="1:16" ht="60" x14ac:dyDescent="0.25">
-      <c r="A12" s="47" t="s">
+      <c r="A12" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="56"/>
+      <c r="B12" s="49"/>
       <c r="C12" s="3" t="s">
         <v>14</v>
       </c>
@@ -5534,8 +5975,8 @@
       <c r="P12" s="3"/>
     </row>
     <row r="13" spans="1:16" ht="90" x14ac:dyDescent="0.25">
-      <c r="A13" s="49"/>
-      <c r="B13" s="58"/>
+      <c r="A13" s="42"/>
+      <c r="B13" s="51"/>
       <c r="C13" s="3" t="s">
         <v>16</v>
       </c>
@@ -5705,10 +6146,10 @@
       <c r="R2" s="3"/>
     </row>
     <row r="3" spans="1:18" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="40" t="s">
         <v>102</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -5720,10 +6161,10 @@
       <c r="E3" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="F3" s="47" t="s">
+      <c r="F3" s="40" t="s">
         <v>145</v>
       </c>
-      <c r="G3" s="47" t="s">
+      <c r="G3" s="40" t="s">
         <v>146</v>
       </c>
       <c r="H3" s="4" t="s">
@@ -5751,8 +6192,8 @@
       <c r="R3" s="3"/>
     </row>
     <row r="4" spans="1:18" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="48"/>
-      <c r="B4" s="48"/>
+      <c r="A4" s="41"/>
+      <c r="B4" s="41"/>
       <c r="C4" s="4" t="s">
         <v>135</v>
       </c>
@@ -5762,8 +6203,8 @@
       <c r="E4" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="4" t="s">
@@ -5789,8 +6230,8 @@
       <c r="R4" s="3"/>
     </row>
     <row r="5" spans="1:18" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="49"/>
-      <c r="B5" s="49"/>
+      <c r="A5" s="42"/>
+      <c r="B5" s="42"/>
       <c r="C5" s="4" t="s">
         <v>136</v>
       </c>
@@ -5800,8 +6241,8 @@
       <c r="E5" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="F5" s="49"/>
-      <c r="G5" s="49"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
       <c r="H5" s="3" t="s">
         <v>127</v>
       </c>
@@ -5819,10 +6260,10 @@
       <c r="R5" s="3"/>
     </row>
     <row r="6" spans="1:18" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="52" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="59" t="s">
+      <c r="B6" s="52" t="s">
         <v>104</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -5855,8 +6296,8 @@
       <c r="R6" s="3"/>
     </row>
     <row r="7" spans="1:18" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="59"/>
-      <c r="B7" s="59"/>
+      <c r="A7" s="52"/>
+      <c r="B7" s="52"/>
       <c r="C7" s="4" t="s">
         <v>138</v>
       </c>
@@ -5881,8 +6322,8 @@
       <c r="R7" s="3"/>
     </row>
     <row r="8" spans="1:18" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="59"/>
-      <c r="B8" s="59"/>
+      <c r="A8" s="52"/>
+      <c r="B8" s="52"/>
       <c r="C8" s="4" t="s">
         <v>139</v>
       </c>
@@ -5909,8 +6350,8 @@
       <c r="R8" s="3"/>
     </row>
     <row r="9" spans="1:18" ht="105" x14ac:dyDescent="0.25">
-      <c r="A9" s="59"/>
-      <c r="B9" s="59"/>
+      <c r="A9" s="52"/>
+      <c r="B9" s="52"/>
       <c r="C9" s="4" t="s">
         <v>107</v>
       </c>
@@ -5939,10 +6380,10 @@
       <c r="R9" s="3"/>
     </row>
     <row r="10" spans="1:18" ht="105" x14ac:dyDescent="0.25">
-      <c r="A10" s="53" t="s">
+      <c r="A10" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="40" t="s">
         <v>111</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -5979,8 +6420,8 @@
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:18" ht="105" x14ac:dyDescent="0.25">
-      <c r="A11" s="54"/>
-      <c r="B11" s="48"/>
+      <c r="A11" s="47"/>
+      <c r="B11" s="41"/>
       <c r="C11" s="3" t="s">
         <v>115</v>
       </c>
@@ -6013,8 +6454,8 @@
       <c r="R11" s="3"/>
     </row>
     <row r="12" spans="1:18" ht="105" x14ac:dyDescent="0.25">
-      <c r="A12" s="55"/>
-      <c r="B12" s="49"/>
+      <c r="A12" s="48"/>
+      <c r="B12" s="42"/>
       <c r="C12" s="3" t="s">
         <v>116</v>
       </c>
@@ -6162,7 +6603,7 @@
       <c r="F2" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="G2" s="40" t="s">
         <v>196</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -6206,7 +6647,7 @@
       <c r="F3" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="G3" s="54"/>
+      <c r="G3" s="47"/>
       <c r="H3" s="12" t="s">
         <v>106</v>
       </c>
@@ -6246,7 +6687,7 @@
       <c r="F4" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="G4" s="54"/>
+      <c r="G4" s="47"/>
       <c r="H4" s="11" t="s">
         <v>191</v>
       </c>
@@ -6290,7 +6731,7 @@
       <c r="F5" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="G5" s="55"/>
+      <c r="G5" s="48"/>
       <c r="H5" s="3" t="s">
         <v>174</v>
       </c>
